--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF38328F-5DCB-4324-8225-CBD6D3C19A07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C19513-3C2A-47E0-B08F-C4D1684F113D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -389,6 +389,30 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -396,30 +420,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -825,7 +825,7 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="32" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -857,7 +857,7 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="34"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -887,7 +887,7 @@
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="34"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -907,16 +907,16 @@
       <c r="H4" s="5">
         <v>15</v>
       </c>
-      <c r="I4" s="38">
-        <v>8</v>
-      </c>
-      <c r="J4" s="38">
+      <c r="I4" s="31">
+        <v>8</v>
+      </c>
+      <c r="J4" s="31">
         <v>5</v>
       </c>
       <c r="K4" s="5">
         <v>15</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>10</v>
       </c>
       <c r="M4" s="6">
@@ -927,7 +927,7 @@
       <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="34"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -950,13 +950,13 @@
       <c r="I5" s="5">
         <v>12</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="31">
         <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>17</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="31">
         <v>15</v>
       </c>
       <c r="M5" s="6">
@@ -967,7 +967,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="34"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
@@ -993,10 +993,10 @@
       <c r="J6" s="5">
         <v>8</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="31">
         <v>16</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="31">
         <v>8</v>
       </c>
       <c r="M6" s="6">
@@ -1007,7 +1007,7 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="34"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
@@ -1037,7 +1037,7 @@
       <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="34"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="34"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1097,7 +1097,7 @@
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="34"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1127,7 +1127,7 @@
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="34"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1157,7 +1157,7 @@
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="34"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1187,7 +1187,7 @@
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="34"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1217,7 +1217,7 @@
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="34"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1247,7 +1247,7 @@
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="34"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1277,7 +1277,7 @@
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="34"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="34"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="34"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1367,7 +1367,7 @@
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="34"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
@@ -1408,8 +1408,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
-  <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.875" style="1"/>
     <col min="2" max="2" width="8.875" style="2"/>
@@ -1477,7 +1477,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -1509,7 +1509,7 @@
       <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="40"/>
+      <c r="A3" s="34"/>
       <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="40"/>
+      <c r="A4" s="34"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
@@ -1562,13 +1562,13 @@
       <c r="I4" s="13">
         <v>12</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="31">
         <v>1</v>
       </c>
       <c r="K4" s="13">
         <v>17</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>15</v>
       </c>
       <c r="M4" s="14">
@@ -1579,7 +1579,7 @@
       <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="40"/>
+      <c r="A5" s="34"/>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
@@ -1619,7 +1619,7 @@
       <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="40"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
@@ -1645,10 +1645,10 @@
       <c r="J6" s="13">
         <v>8</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="31">
         <v>16</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="31">
         <v>18</v>
       </c>
       <c r="M6" s="14">
@@ -1659,7 +1659,7 @@
       <c r="P6" s="16"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1">
-      <c r="A7" s="40"/>
+      <c r="A7" s="34"/>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
@@ -1679,16 +1679,16 @@
       <c r="H7" s="13">
         <v>18</v>
       </c>
-      <c r="I7" s="38">
-        <v>8</v>
-      </c>
-      <c r="J7" s="38">
+      <c r="I7" s="31">
+        <v>8</v>
+      </c>
+      <c r="J7" s="31">
         <v>10</v>
       </c>
       <c r="K7" s="13">
         <v>10</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="31">
         <v>16</v>
       </c>
       <c r="M7" s="13"/>
@@ -1697,7 +1697,7 @@
       <c r="P7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1">
-      <c r="A8" s="40"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
@@ -1717,7 +1717,7 @@
       <c r="H8" s="13">
         <v>0</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="31">
         <v>5</v>
       </c>
       <c r="J8" s="13">
@@ -1737,7 +1737,7 @@
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
-      <c r="A9" s="40"/>
+      <c r="A9" s="34"/>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
@@ -1766,7 +1766,7 @@
       <c r="K9" s="13">
         <v>24</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="31">
         <v>21</v>
       </c>
       <c r="M9" s="14">
@@ -1777,7 +1777,7 @@
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1">
-      <c r="A10" s="40"/>
+      <c r="A10" s="34"/>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
@@ -1797,10 +1797,10 @@
       <c r="H10" s="13">
         <v>0</v>
       </c>
-      <c r="I10" s="38">
-        <v>11</v>
-      </c>
-      <c r="J10" s="38">
+      <c r="I10" s="31">
+        <v>11</v>
+      </c>
+      <c r="J10" s="31">
         <v>0</v>
       </c>
       <c r="K10" s="13">
@@ -1817,7 +1817,7 @@
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1">
-      <c r="A11" s="40"/>
+      <c r="A11" s="34"/>
       <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
@@ -1847,7 +1847,7 @@
       <c r="P11" s="18"/>
     </row>
     <row r="12" spans="1:16" ht="15" customHeight="1">
-      <c r="A12" s="40"/>
+      <c r="A12" s="34"/>
       <c r="B12" s="11" t="s">
         <v>12</v>
       </c>
@@ -1877,7 +1877,7 @@
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1">
-      <c r="A13" s="40"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
@@ -1907,7 +1907,7 @@
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1">
-      <c r="A14" s="40"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
@@ -1937,7 +1937,7 @@
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="40"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
@@ -1967,7 +1967,7 @@
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1">
-      <c r="A16" s="40"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
@@ -1997,7 +1997,7 @@
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1">
-      <c r="A17" s="40"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
@@ -2027,7 +2027,7 @@
       <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1">
-      <c r="A18" s="40"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1">
-      <c r="A19" s="40"/>
+      <c r="A19" s="34"/>
       <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
@@ -2086,8 +2086,8 @@
       <c r="O19" s="14"/>
       <c r="P19" s="13"/>
     </row>
-    <row r="20" spans="1:16" ht="15">
-      <c r="A20" s="40"/>
+    <row r="20" spans="1:16">
+      <c r="A20" s="34"/>
       <c r="B20" s="11" t="s">
         <v>12</v>
       </c>
@@ -2116,8 +2116,8 @@
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
     </row>
-    <row r="21" spans="1:16" ht="15">
-      <c r="A21" s="41"/>
+    <row r="21" spans="1:16">
+      <c r="A21" s="35"/>
       <c r="B21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2146,20 +2146,6 @@
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
     </row>
-    <row r="22" spans="1:16" ht="15"/>
-    <row r="23" spans="1:16" ht="15"/>
-    <row r="24" spans="1:16" ht="15"/>
-    <row r="25" spans="1:16" ht="15"/>
-    <row r="26" spans="1:16" ht="15"/>
-    <row r="27" spans="1:16" ht="15"/>
-    <row r="28" spans="1:16" ht="15"/>
-    <row r="29" spans="1:16" ht="15"/>
-    <row r="30" spans="1:16" ht="15"/>
-    <row r="31" spans="1:16" ht="15"/>
-    <row r="32" spans="1:16" ht="15"/>
-    <row r="33" ht="15"/>
-    <row r="34" ht="15"/>
-    <row r="35" ht="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A21"/>
@@ -2170,8 +2156,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.875" style="1"/>
     <col min="2" max="2" width="8.875" style="2"/>
@@ -2239,7 +2225,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="36" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -2271,7 +2257,7 @@
       <c r="P2" s="21"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="36"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="19" t="s">
         <v>11</v>
       </c>
@@ -2291,16 +2277,16 @@
       <c r="H3" s="21">
         <v>15</v>
       </c>
-      <c r="I3" s="38">
-        <v>8</v>
-      </c>
-      <c r="J3" s="38">
+      <c r="I3" s="31">
+        <v>8</v>
+      </c>
+      <c r="J3" s="31">
         <v>5</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="31">
         <v>15</v>
       </c>
-      <c r="L3" s="38">
+      <c r="L3" s="31">
         <v>10</v>
       </c>
       <c r="M3" s="22">
@@ -2311,7 +2297,7 @@
       <c r="P3" s="21"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="36"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="19" t="s">
         <v>11</v>
       </c>
@@ -2331,16 +2317,16 @@
       <c r="H4" s="21">
         <v>18</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="31">
         <v>12</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="31">
         <v>1</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>17</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>15</v>
       </c>
       <c r="M4" s="22">
@@ -2351,7 +2337,7 @@
       <c r="P4" s="21"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="36"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="19" t="s">
         <v>11</v>
       </c>
@@ -2381,7 +2367,7 @@
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="37"/>
+      <c r="A6" s="38"/>
       <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
@@ -2410,55 +2396,6 @@
       <c r="O6" s="22"/>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="15"/>
-    <row r="8" spans="1:16" ht="15"/>
-    <row r="9" spans="1:16" ht="15"/>
-    <row r="10" spans="1:16" ht="15"/>
-    <row r="11" spans="1:16" ht="15"/>
-    <row r="12" spans="1:16" ht="15"/>
-    <row r="13" spans="1:16" ht="15"/>
-    <row r="14" spans="1:16" ht="15"/>
-    <row r="15" spans="1:16" ht="15"/>
-    <row r="16" spans="1:16" ht="15"/>
-    <row r="17" ht="15"/>
-    <row r="18" ht="15"/>
-    <row r="19" ht="15"/>
-    <row r="20" ht="15"/>
-    <row r="21" ht="15"/>
-    <row r="22" ht="15"/>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15"/>
-    <row r="25" ht="15"/>
-    <row r="26" ht="15"/>
-    <row r="27" ht="15"/>
-    <row r="28" ht="15"/>
-    <row r="29" ht="15"/>
-    <row r="30" ht="15"/>
-    <row r="31" ht="15"/>
-    <row r="32" ht="15"/>
-    <row r="33" ht="15"/>
-    <row r="34" ht="15"/>
-    <row r="35" ht="15"/>
-    <row r="36" ht="15"/>
-    <row r="37" ht="15"/>
-    <row r="38" ht="15"/>
-    <row r="39" ht="15"/>
-    <row r="40" ht="15"/>
-    <row r="41" ht="15"/>
-    <row r="42" ht="15"/>
-    <row r="43" ht="15"/>
-    <row r="44" ht="15"/>
-    <row r="45" ht="15"/>
-    <row r="46" ht="15"/>
-    <row r="47" ht="15"/>
-    <row r="48" ht="15"/>
-    <row r="49" ht="15"/>
-    <row r="50" ht="15"/>
-    <row r="51" ht="15"/>
-    <row r="52" ht="15"/>
-    <row r="53" ht="15"/>
-    <row r="54" ht="15"/>
-    <row r="55" ht="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A6"/>
@@ -2469,8 +2406,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
-  <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.875" style="1"/>
     <col min="2" max="2" width="8.875" style="2"/>
@@ -2538,7 +2475,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -2570,7 +2507,7 @@
       <c r="P2" s="25"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="32"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="24" t="s">
         <v>11</v>
       </c>
@@ -2590,16 +2527,16 @@
       <c r="H3" s="26">
         <v>15</v>
       </c>
-      <c r="I3" s="38">
-        <v>8</v>
-      </c>
-      <c r="J3" s="38">
+      <c r="I3" s="31">
+        <v>8</v>
+      </c>
+      <c r="J3" s="31">
         <v>5</v>
       </c>
-      <c r="K3" s="38">
+      <c r="K3" s="31">
         <v>15</v>
       </c>
-      <c r="L3" s="38">
+      <c r="L3" s="31">
         <v>10</v>
       </c>
       <c r="M3" s="27">
@@ -2610,7 +2547,7 @@
       <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="32"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
@@ -2630,16 +2567,16 @@
       <c r="H4" s="26">
         <v>18</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="31">
         <v>12</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="31">
         <v>1</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="31">
         <v>17</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>15</v>
       </c>
       <c r="M4" s="27">
@@ -2650,7 +2587,7 @@
       <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="32"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -2680,7 +2617,7 @@
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="33"/>
+      <c r="A6" s="41"/>
       <c r="B6" s="24" t="s">
         <v>11</v>
       </c>
@@ -2709,55 +2646,6 @@
       <c r="O6" s="27"/>
       <c r="P6" s="26"/>
     </row>
-    <row r="7" spans="1:16" ht="15"/>
-    <row r="8" spans="1:16" ht="15"/>
-    <row r="9" spans="1:16" ht="15"/>
-    <row r="10" spans="1:16" ht="15"/>
-    <row r="11" spans="1:16" ht="15"/>
-    <row r="12" spans="1:16" ht="15"/>
-    <row r="13" spans="1:16" ht="15"/>
-    <row r="14" spans="1:16" ht="15"/>
-    <row r="15" spans="1:16" ht="15"/>
-    <row r="16" spans="1:16" ht="15"/>
-    <row r="17" ht="15"/>
-    <row r="18" ht="15"/>
-    <row r="19" ht="15"/>
-    <row r="20" ht="15"/>
-    <row r="21" ht="15"/>
-    <row r="22" ht="15"/>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15"/>
-    <row r="25" ht="15"/>
-    <row r="26" ht="15"/>
-    <row r="27" ht="15"/>
-    <row r="28" ht="15"/>
-    <row r="29" ht="15"/>
-    <row r="30" ht="15"/>
-    <row r="31" ht="15"/>
-    <row r="32" ht="15"/>
-    <row r="33" ht="15"/>
-    <row r="34" ht="15"/>
-    <row r="35" ht="15"/>
-    <row r="36" ht="15"/>
-    <row r="37" ht="15"/>
-    <row r="38" ht="15"/>
-    <row r="39" ht="15"/>
-    <row r="40" ht="15"/>
-    <row r="41" ht="15"/>
-    <row r="42" ht="15"/>
-    <row r="43" ht="15"/>
-    <row r="44" ht="15"/>
-    <row r="45" ht="15"/>
-    <row r="46" ht="15"/>
-    <row r="47" ht="15"/>
-    <row r="48" ht="15"/>
-    <row r="49" ht="15"/>
-    <row r="50" ht="15"/>
-    <row r="51" ht="15"/>
-    <row r="52" ht="15"/>
-    <row r="53" ht="15"/>
-    <row r="54" ht="15"/>
-    <row r="55" ht="15"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A6"/>
@@ -2767,12 +2655,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2960,19 +2849,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2996,17 +2892,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C19513-3C2A-47E0-B08F-C4D1684F113D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8EC48C-8DFF-4EC9-9C3F-501FD289C23B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="29">
   <si>
     <t>MOD.</t>
   </si>
@@ -109,12 +109,6 @@
   </si>
   <si>
     <t>VIATURA PA</t>
-  </si>
-  <si>
-    <t>24 / onibus</t>
-  </si>
-  <si>
-    <t>24/ONIBUS</t>
   </si>
   <si>
     <t>1S</t>
@@ -757,26 +751,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="5"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -926,7 +920,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
@@ -1177,11 +1171,21 @@
       <c r="H12" s="5">
         <v>0</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
+      <c r="I12" s="5">
+        <v>2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>4</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
+        <v>45798</v>
+      </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="5"/>
@@ -1204,14 +1208,24 @@
       <c r="G13" s="5">
         <v>4</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="H13" s="5">
+        <v>24</v>
+      </c>
+      <c r="I13" s="5">
+        <v>16</v>
+      </c>
+      <c r="J13" s="5">
+        <v>14</v>
+      </c>
+      <c r="K13" s="5">
+        <v>4</v>
+      </c>
+      <c r="L13" s="31">
+        <v>20</v>
+      </c>
+      <c r="M13" s="6">
+        <v>45798</v>
+      </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="5"/>
@@ -1409,26 +1423,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="13"/>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1443,7 +1457,7 @@
         <v>18</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>20</v>
@@ -1867,11 +1881,21 @@
       <c r="H12" s="13">
         <v>0</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="I12" s="13">
+        <v>2</v>
+      </c>
+      <c r="J12" s="13">
+        <v>4</v>
+      </c>
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="14">
+        <v>45798</v>
+      </c>
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
       <c r="P12" s="13"/>
@@ -1894,14 +1918,24 @@
       <c r="G13" s="13">
         <v>4</v>
       </c>
-      <c r="H13" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="H13" s="13">
+        <v>24</v>
+      </c>
+      <c r="I13" s="13">
+        <v>16</v>
+      </c>
+      <c r="J13" s="13">
+        <v>14</v>
+      </c>
+      <c r="K13" s="13">
+        <v>4</v>
+      </c>
+      <c r="L13" s="31">
+        <v>20</v>
+      </c>
+      <c r="M13" s="14">
+        <v>45798</v>
+      </c>
       <c r="N13" s="14"/>
       <c r="O13" s="14"/>
       <c r="P13" s="13"/>
@@ -2017,11 +2051,21 @@
       <c r="H17" s="13">
         <v>0</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="I17" s="31">
+        <v>5</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14">
+        <v>45798</v>
+      </c>
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
       <c r="P17" s="13"/>
@@ -2157,26 +2201,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="21"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2232,7 +2276,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" s="20"/>
       <c r="E2" s="21">
@@ -2407,26 +2451,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="26"/>
       <c r="B1" s="24" t="s">
         <v>0</v>
@@ -2482,7 +2526,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="26">
@@ -2655,13 +2699,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2849,26 +2892,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2892,9 +2928,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8EC48C-8DFF-4EC9-9C3F-501FD289C23B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40D3B53-5A9D-4BEC-B1C2-FAFCCDC2F2A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
@@ -1341,11 +1341,21 @@
       <c r="H17" s="5">
         <v>20</v>
       </c>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="I17" s="5">
+        <v>10</v>
+      </c>
+      <c r="J17" s="5">
+        <v>8</v>
+      </c>
+      <c r="K17" s="31">
+        <v>10</v>
+      </c>
+      <c r="L17" s="31">
+        <v>13</v>
+      </c>
+      <c r="M17" s="6">
+        <v>45798</v>
+      </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="5"/>
@@ -2091,11 +2101,21 @@
       <c r="H18" s="13">
         <v>20</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="I18" s="13">
+        <v>10</v>
+      </c>
+      <c r="J18" s="13">
+        <v>8</v>
+      </c>
+      <c r="K18" s="31">
+        <v>10</v>
+      </c>
+      <c r="L18" s="31">
+        <v>13</v>
+      </c>
+      <c r="M18" s="14">
+        <v>45798</v>
+      </c>
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
       <c r="P18" s="13"/>
@@ -2699,12 +2719,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2892,19 +2913,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2928,17 +2956,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40D3B53-5A9D-4BEC-B1C2-FAFCCDC2F2A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB81107E-D9E8-4A53-9A5C-4535DF2B2B03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
@@ -1021,10 +1021,18 @@
       <c r="H7" s="5">
         <v>18</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
+      <c r="I7" s="31">
+        <v>8</v>
+      </c>
+      <c r="J7" s="31">
+        <v>10</v>
+      </c>
+      <c r="K7" s="5">
+        <v>10</v>
+      </c>
+      <c r="L7" s="31">
+        <v>16</v>
+      </c>
       <c r="M7" s="5"/>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -1251,11 +1259,21 @@
       <c r="H14" s="5">
         <v>0</v>
       </c>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>4</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="6">
+        <v>45798</v>
+      </c>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="5"/>
@@ -2719,13 +2737,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2913,26 +2930,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2956,9 +2966,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB81107E-D9E8-4A53-9A5C-4535DF2B2B03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C57BF-05BD-44CD-A5B4-48E1058C5199}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
@@ -1033,7 +1033,9 @@
       <c r="L7" s="31">
         <v>16</v>
       </c>
-      <c r="M7" s="5"/>
+      <c r="M7" s="6">
+        <v>45798</v>
+      </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="9"/>
@@ -2737,12 +2739,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2930,19 +2933,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2966,17 +2976,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C57BF-05BD-44CD-A5B4-48E1058C5199}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11555ACC-1D7F-4686-855C-24A131B7FEC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="1" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -751,26 +751,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="5"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -920,7 +920,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="14.5">
+    <row r="5" spans="1:16">
       <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
@@ -1453,26 +1453,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="13"/>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1735,7 +1735,9 @@
       <c r="L7" s="31">
         <v>16</v>
       </c>
-      <c r="M7" s="13"/>
+      <c r="M7" s="14">
+        <v>45798</v>
+      </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
       <c r="P7" s="17"/>
@@ -2241,26 +2243,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="21"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2491,26 +2493,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="26"/>
       <c r="B1" s="24" t="s">
         <v>0</v>
@@ -2739,13 +2741,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2933,26 +2934,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2976,9 +2970,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11555ACC-1D7F-4686-855C-24A131B7FEC7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B7EAE-B568-426F-AFE8-182000A3BF07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="1" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -1061,11 +1061,21 @@
       <c r="H8" s="5">
         <v>23</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="I8" s="5">
+        <v>11</v>
+      </c>
+      <c r="J8" s="5">
+        <v>8</v>
+      </c>
+      <c r="K8" s="5">
+        <v>24</v>
+      </c>
+      <c r="L8" s="5">
+        <v>21</v>
+      </c>
+      <c r="M8" s="6">
+        <v>45799</v>
+      </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="5"/>
@@ -1091,11 +1101,21 @@
       <c r="H9" s="5">
         <v>0</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="I9" s="5">
+        <v>10</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>8</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <v>45799</v>
+      </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="5"/>
@@ -1121,11 +1141,21 @@
       <c r="H10" s="5">
         <v>0</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <v>45799</v>
+      </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="5"/>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912B7EAE-B568-426F-AFE8-182000A3BF07}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FFD427-B380-4669-8EA7-A3AB34CD4A33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -751,26 +751,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="5"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -920,7 +920,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
@@ -1181,11 +1181,21 @@
       <c r="H11" s="5">
         <v>0</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
+      <c r="I11" s="5">
+        <v>11</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
+        <v>45799</v>
+      </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="10"/>
@@ -1483,26 +1493,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="13"/>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1913,11 +1923,21 @@
       <c r="H11" s="13">
         <v>0</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="I11" s="13">
+        <v>11</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>45799</v>
+      </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
       <c r="P11" s="18"/>
@@ -2273,26 +2293,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="21"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2523,26 +2543,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="26"/>
       <c r="B1" s="24" t="s">
         <v>0</v>
@@ -2771,12 +2791,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2964,19 +2985,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3000,17 +3028,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FFD427-B380-4669-8EA7-A3AB34CD4A33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87FE834-EDD1-4831-BACF-B9FD3CD757BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="48">
   <si>
     <t>MOD.</t>
   </si>
@@ -115,6 +115,63 @@
   </si>
   <si>
     <t>MONITORES  PD</t>
+  </si>
+  <si>
+    <t>LOULY / JOANA / PERUCH</t>
+  </si>
+  <si>
+    <t>CAMILA</t>
+  </si>
+  <si>
+    <t>MARCEL/CAMILA / KASSIA</t>
+  </si>
+  <si>
+    <t>CAMILA / KASSIA</t>
+  </si>
+  <si>
+    <t>LUCIANA /CAMILA</t>
+  </si>
+  <si>
+    <t>MARCEl E KALIL</t>
+  </si>
+  <si>
+    <t>JOANA / BELMIRO</t>
+  </si>
+  <si>
+    <t>LOULY/CAMILA</t>
+  </si>
+  <si>
+    <t>MARCEL / JOANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTO, LAGO </t>
+  </si>
+  <si>
+    <t>ROBERTO E FABIANA.</t>
+  </si>
+  <si>
+    <t>BELMIRO / KASSIA</t>
+  </si>
+  <si>
+    <t>SABRINA E CAMILA</t>
+  </si>
+  <si>
+    <t>MAZOTTI</t>
+  </si>
+  <si>
+    <t>LUCIANA/CAMILA</t>
+  </si>
+  <si>
+    <t>BELMIRO</t>
+  </si>
+  <si>
+    <t>ARTHUR / CRISTIANO</t>
+  </si>
+  <si>
+    <t>DANIELE</t>
+  </si>
+  <si>
+    <t>KALIL</t>
   </si>
 </sst>
 </file>
@@ -227,7 +284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -287,11 +344,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -415,6 +485,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,7 +835,7 @@
     <col min="1" max="1" width="8.83203125" style="1"/>
     <col min="2" max="2" width="8.83203125" style="2"/>
     <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
@@ -818,7 +897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" ht="42">
       <c r="A2" s="32" t="s">
         <v>14</v>
       </c>
@@ -828,7 +907,9 @@
       <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="42" t="s">
+        <v>29</v>
+      </c>
       <c r="E2" s="5">
         <v>9</v>
       </c>
@@ -858,7 +939,9 @@
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E3" s="5">
         <v>9</v>
       </c>
@@ -880,7 +963,7 @@
       <c r="O3" s="6"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" ht="28">
       <c r="A4" s="32"/>
       <c r="B4" s="3" t="s">
         <v>11</v>
@@ -888,7 +971,9 @@
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="42" t="s">
+        <v>31</v>
+      </c>
       <c r="E4" s="5">
         <v>13</v>
       </c>
@@ -928,7 +1013,9 @@
       <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="43" t="s">
+        <v>32</v>
+      </c>
       <c r="E5" s="7">
         <v>12</v>
       </c>
@@ -960,7 +1047,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" ht="28">
       <c r="A6" s="32"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -968,7 +1055,9 @@
       <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="42" t="s">
+        <v>33</v>
+      </c>
       <c r="E6" s="5">
         <v>10</v>
       </c>
@@ -1008,7 +1097,9 @@
       <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="43" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="5">
         <v>13</v>
       </c>
@@ -1048,7 +1139,9 @@
       <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="43" t="s">
+        <v>35</v>
+      </c>
       <c r="E8" s="5">
         <v>11</v>
       </c>
@@ -1088,7 +1181,9 @@
       <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="43" t="s">
+        <v>35</v>
+      </c>
       <c r="E9" s="5">
         <v>10</v>
       </c>
@@ -1128,7 +1223,9 @@
       <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="43" t="s">
+        <v>35</v>
+      </c>
       <c r="E10" s="5">
         <v>5</v>
       </c>
@@ -1168,7 +1265,9 @@
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E11" s="5">
         <v>11</v>
       </c>
@@ -1208,7 +1307,9 @@
       <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E12" s="5">
         <v>2</v>
       </c>
@@ -1248,7 +1349,9 @@
       <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E13" s="5">
         <v>16</v>
       </c>
@@ -1288,7 +1391,9 @@
       <c r="C14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="43" t="s">
+        <v>36</v>
+      </c>
       <c r="E14" s="5">
         <v>2</v>
       </c>
@@ -1328,7 +1433,9 @@
       <c r="C15" s="3">
         <v>5</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="42" t="s">
+        <v>37</v>
+      </c>
       <c r="E15" s="5">
         <v>5</v>
       </c>
@@ -1358,7 +1465,9 @@
       <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="42" t="s">
+        <v>38</v>
+      </c>
       <c r="E16" s="5">
         <v>4</v>
       </c>
@@ -1388,7 +1497,9 @@
       <c r="C17" s="3">
         <v>7</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E17" s="5">
         <v>10</v>
       </c>
@@ -1420,7 +1531,7 @@
       <c r="O17" s="6"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16">
+    <row r="18" spans="1:16" ht="28">
       <c r="A18" s="32"/>
       <c r="B18" s="3" t="s">
         <v>12</v>
@@ -1428,7 +1539,9 @@
       <c r="C18" s="3">
         <v>8</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="42" t="s">
+        <v>39</v>
+      </c>
       <c r="E18" s="5">
         <v>9</v>
       </c>
@@ -1458,7 +1571,7 @@
       <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="5">
         <v>6</v>
       </c>
@@ -1560,7 +1673,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1">
+    <row r="2" spans="1:16" ht="28">
       <c r="A2" s="33" t="s">
         <v>15</v>
       </c>
@@ -1570,7 +1683,9 @@
       <c r="C2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="12"/>
+      <c r="D2" s="42" t="s">
+        <v>40</v>
+      </c>
       <c r="E2" s="13">
         <v>9</v>
       </c>
@@ -1592,7 +1707,7 @@
       <c r="O2" s="14"/>
       <c r="P2" s="13"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1">
+    <row r="3" spans="1:16" ht="28">
       <c r="A3" s="34"/>
       <c r="B3" s="11" t="s">
         <v>9</v>
@@ -1600,7 +1715,9 @@
       <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="42" t="s">
+        <v>41</v>
+      </c>
       <c r="E3" s="13">
         <v>15</v>
       </c>
@@ -1622,7 +1739,7 @@
       <c r="O3" s="14"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1">
+    <row r="4" spans="1:16">
       <c r="A4" s="34"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
@@ -1630,7 +1747,9 @@
       <c r="C4" s="11">
         <v>1</v>
       </c>
-      <c r="D4" s="12"/>
+      <c r="D4" s="42" t="s">
+        <v>30</v>
+      </c>
       <c r="E4" s="13">
         <v>12</v>
       </c>
@@ -1662,7 +1781,7 @@
       <c r="O4" s="14"/>
       <c r="P4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1">
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="34"/>
       <c r="B5" s="11" t="s">
         <v>11</v>
@@ -1670,7 +1789,9 @@
       <c r="C5" s="11">
         <v>2</v>
       </c>
-      <c r="D5" s="12"/>
+      <c r="D5" s="43" t="s">
+        <v>42</v>
+      </c>
       <c r="E5" s="15">
         <v>6</v>
       </c>
@@ -1702,7 +1823,7 @@
       <c r="O5" s="14"/>
       <c r="P5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1">
+    <row r="6" spans="1:16" ht="28">
       <c r="A6" s="34"/>
       <c r="B6" s="11" t="s">
         <v>11</v>
@@ -1710,7 +1831,9 @@
       <c r="C6" s="11">
         <v>3</v>
       </c>
-      <c r="D6" s="12"/>
+      <c r="D6" s="42" t="s">
+        <v>43</v>
+      </c>
       <c r="E6" s="13">
         <v>10</v>
       </c>
@@ -1742,7 +1865,7 @@
       <c r="O6" s="14"/>
       <c r="P6" s="16"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1">
+    <row r="7" spans="1:16">
       <c r="A7" s="34"/>
       <c r="B7" s="11" t="s">
         <v>11</v>
@@ -1750,7 +1873,9 @@
       <c r="C7" s="11">
         <v>4</v>
       </c>
-      <c r="D7" s="12"/>
+      <c r="D7" s="44" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="13">
         <v>13</v>
       </c>
@@ -1782,7 +1907,7 @@
       <c r="O7" s="14"/>
       <c r="P7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1">
+    <row r="8" spans="1:16">
       <c r="A8" s="34"/>
       <c r="B8" s="11" t="s">
         <v>11</v>
@@ -1790,7 +1915,9 @@
       <c r="C8" s="11">
         <v>5</v>
       </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="43" t="s">
+        <v>44</v>
+      </c>
       <c r="E8" s="13">
         <v>6</v>
       </c>
@@ -1822,7 +1949,7 @@
       <c r="O8" s="14"/>
       <c r="P8" s="13"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1">
+    <row r="9" spans="1:16">
       <c r="A9" s="34"/>
       <c r="B9" s="11" t="s">
         <v>11</v>
@@ -1830,7 +1957,9 @@
       <c r="C9" s="11">
         <v>6</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="43" t="s">
+        <v>44</v>
+      </c>
       <c r="E9" s="13">
         <v>11</v>
       </c>
@@ -1862,7 +1991,7 @@
       <c r="O9" s="14"/>
       <c r="P9" s="13"/>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1">
+    <row r="10" spans="1:16">
       <c r="A10" s="34"/>
       <c r="B10" s="11" t="s">
         <v>11</v>
@@ -1870,7 +1999,9 @@
       <c r="C10" s="11">
         <v>7</v>
       </c>
-      <c r="D10" s="12"/>
+      <c r="D10" s="42" t="s">
+        <v>44</v>
+      </c>
       <c r="E10" s="13">
         <v>10</v>
       </c>
@@ -1902,7 +2033,7 @@
       <c r="O10" s="14"/>
       <c r="P10" s="13"/>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1">
+    <row r="11" spans="1:16">
       <c r="A11" s="34"/>
       <c r="B11" s="11" t="s">
         <v>12</v>
@@ -1910,7 +2041,9 @@
       <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D11" s="12"/>
+      <c r="D11" s="42" t="s">
+        <v>30</v>
+      </c>
       <c r="E11" s="13">
         <v>11</v>
       </c>
@@ -1942,7 +2075,7 @@
       <c r="O11" s="14"/>
       <c r="P11" s="18"/>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1">
+    <row r="12" spans="1:16">
       <c r="A12" s="34"/>
       <c r="B12" s="11" t="s">
         <v>12</v>
@@ -1950,7 +2083,9 @@
       <c r="C12" s="11">
         <v>2</v>
       </c>
-      <c r="D12" s="12"/>
+      <c r="D12" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E12" s="13">
         <v>2</v>
       </c>
@@ -1982,7 +2117,7 @@
       <c r="O12" s="14"/>
       <c r="P12" s="13"/>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1">
+    <row r="13" spans="1:16">
       <c r="A13" s="34"/>
       <c r="B13" s="11" t="s">
         <v>12</v>
@@ -1990,7 +2125,9 @@
       <c r="C13" s="11">
         <v>3</v>
       </c>
-      <c r="D13" s="12"/>
+      <c r="D13" s="43" t="s">
+        <v>30</v>
+      </c>
       <c r="E13" s="13">
         <v>16</v>
       </c>
@@ -2022,7 +2159,7 @@
       <c r="O13" s="14"/>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1">
+    <row r="14" spans="1:16" ht="28">
       <c r="A14" s="34"/>
       <c r="B14" s="11" t="s">
         <v>12</v>
@@ -2030,7 +2167,9 @@
       <c r="C14" s="11">
         <v>4</v>
       </c>
-      <c r="D14" s="12"/>
+      <c r="D14" s="42" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="13">
         <v>6</v>
       </c>
@@ -2052,7 +2191,7 @@
       <c r="O14" s="14"/>
       <c r="P14" s="13"/>
     </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1">
+    <row r="15" spans="1:16">
       <c r="A15" s="34"/>
       <c r="B15" s="11" t="s">
         <v>12</v>
@@ -2060,7 +2199,9 @@
       <c r="C15" s="11">
         <v>5</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" s="42" t="s">
+        <v>46</v>
+      </c>
       <c r="E15" s="13">
         <v>8</v>
       </c>
@@ -2082,7 +2223,7 @@
       <c r="O15" s="14"/>
       <c r="P15" s="13"/>
     </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1">
+    <row r="16" spans="1:16">
       <c r="A16" s="34"/>
       <c r="B16" s="11" t="s">
         <v>12</v>
@@ -2090,7 +2231,9 @@
       <c r="C16" s="11">
         <v>6</v>
       </c>
-      <c r="D16" s="12"/>
+      <c r="D16" s="42" t="s">
+        <v>46</v>
+      </c>
       <c r="E16" s="13">
         <v>8</v>
       </c>
@@ -2112,7 +2255,7 @@
       <c r="O16" s="14"/>
       <c r="P16" s="13"/>
     </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1">
+    <row r="17" spans="1:16">
       <c r="A17" s="34"/>
       <c r="B17" s="11" t="s">
         <v>12</v>
@@ -2120,7 +2263,9 @@
       <c r="C17" s="11">
         <v>7</v>
       </c>
-      <c r="D17" s="12"/>
+      <c r="D17" s="42" t="s">
+        <v>47</v>
+      </c>
       <c r="E17" s="13">
         <v>2</v>
       </c>
@@ -2152,7 +2297,7 @@
       <c r="O17" s="14"/>
       <c r="P17" s="13"/>
     </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1">
+    <row r="18" spans="1:16">
       <c r="A18" s="34"/>
       <c r="B18" s="11" t="s">
         <v>12</v>
@@ -2160,7 +2305,9 @@
       <c r="C18" s="11">
         <v>8</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="42" t="s">
+        <v>30</v>
+      </c>
       <c r="E18" s="13">
         <v>10</v>
       </c>
@@ -2192,7 +2339,7 @@
       <c r="O18" s="14"/>
       <c r="P18" s="13"/>
     </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1">
+    <row r="19" spans="1:16">
       <c r="A19" s="34"/>
       <c r="B19" s="11" t="s">
         <v>12</v>
@@ -2200,7 +2347,7 @@
       <c r="C19" s="11">
         <v>9</v>
       </c>
-      <c r="D19" s="12"/>
+      <c r="D19" s="42"/>
       <c r="E19" s="13">
         <v>6</v>
       </c>
@@ -2230,7 +2377,7 @@
       <c r="C20" s="30">
         <v>10</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="43"/>
       <c r="E20" s="13">
         <v>6</v>
       </c>
@@ -2260,7 +2407,7 @@
       <c r="C21" s="30">
         <v>11</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="13">
         <v>1</v>
       </c>
@@ -2791,13 +2938,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2985,26 +3131,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3028,9 +3167,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87FE834-EDD1-4831-BACF-B9FD3CD757BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A20CD7-940C-4B9D-96BC-D80893742B93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
   <si>
     <t>MOD.</t>
   </si>
@@ -172,6 +172,12 @@
   </si>
   <si>
     <t>KALIL</t>
+  </si>
+  <si>
+    <t>TURMA A</t>
+  </si>
+  <si>
+    <t>DAMAZ</t>
   </si>
 </sst>
 </file>
@@ -456,36 +462,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -494,6 +470,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,8 +903,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="42">
-      <c r="A2" s="32" t="s">
+    <row r="2" spans="1:16" ht="28">
+      <c r="A2" s="35" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -907,7 +913,7 @@
       <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="32" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="5">
@@ -932,14 +938,14 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="32"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="5">
@@ -964,14 +970,14 @@
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16" ht="28">
-      <c r="A4" s="32"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="32" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="5">
@@ -1006,14 +1012,14 @@
       <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="32"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="33" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="7">
@@ -1047,15 +1053,15 @@
       <c r="O5" s="6"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" ht="28">
-      <c r="A6" s="32"/>
+    <row r="6" spans="1:16">
+      <c r="A6" s="35"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="32" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="5">
@@ -1090,14 +1096,14 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="32"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="33" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="5">
@@ -1132,14 +1138,14 @@
       <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="32"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="5">
@@ -1174,14 +1180,14 @@
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="32"/>
+      <c r="A9" s="35"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="5">
@@ -1216,14 +1222,14 @@
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="32"/>
+      <c r="A10" s="35"/>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="33" t="s">
         <v>35</v>
       </c>
       <c r="E10" s="5">
@@ -1258,14 +1264,14 @@
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="32"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="5">
@@ -1300,14 +1306,14 @@
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="32"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="5">
@@ -1342,14 +1348,14 @@
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="32"/>
+      <c r="A13" s="35"/>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="5">
@@ -1384,14 +1390,14 @@
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="32"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="33" t="s">
         <v>36</v>
       </c>
       <c r="E14" s="5">
@@ -1426,14 +1432,14 @@
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="32"/>
+      <c r="A15" s="35"/>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3">
         <v>5</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="32" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="5">
@@ -1458,14 +1464,14 @@
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="32"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="32" t="s">
         <v>38</v>
       </c>
       <c r="E16" s="5">
@@ -1490,14 +1496,14 @@
       <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="32"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="3">
         <v>7</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="5">
@@ -1532,14 +1538,14 @@
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16" ht="28">
-      <c r="A18" s="32"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="3">
         <v>8</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="32" t="s">
         <v>39</v>
       </c>
       <c r="E18" s="5">
@@ -1564,14 +1570,14 @@
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="32"/>
+      <c r="A19" s="35"/>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D19" s="43"/>
+      <c r="D19" s="33"/>
       <c r="E19" s="5">
         <v>6</v>
       </c>
@@ -1674,7 +1680,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="28">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -1683,7 +1689,7 @@
       <c r="C2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="E2" s="13">
@@ -1708,14 +1714,14 @@
       <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:16" ht="28">
-      <c r="A3" s="34"/>
+      <c r="A3" s="37"/>
       <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="32" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="13">
@@ -1740,14 +1746,14 @@
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="34"/>
+      <c r="A4" s="37"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="11">
         <v>1</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="13">
@@ -1782,14 +1788,14 @@
       <c r="P4" s="13"/>
     </row>
     <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="34"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11">
         <v>2</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="33" t="s">
         <v>42</v>
       </c>
       <c r="E5" s="15">
@@ -1824,14 +1830,14 @@
       <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:16" ht="28">
-      <c r="A6" s="34"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11">
         <v>3</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="32" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="13">
@@ -1866,14 +1872,14 @@
       <c r="P6" s="16"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="34"/>
+      <c r="A7" s="37"/>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="11">
         <v>4</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="34" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="13">
@@ -1908,14 +1914,14 @@
       <c r="P7" s="17"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="34"/>
+      <c r="A8" s="37"/>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="11">
         <v>5</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="33" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="13">
@@ -1950,14 +1956,14 @@
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="34"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="11">
         <v>6</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="33" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="13">
@@ -1992,14 +1998,14 @@
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="34"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="11">
         <v>7</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="32" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="13">
@@ -2034,14 +2040,14 @@
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="34"/>
+      <c r="A11" s="37"/>
       <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="11">
         <v>1</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="13">
@@ -2076,14 +2082,14 @@
       <c r="P11" s="18"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="34"/>
+      <c r="A12" s="37"/>
       <c r="B12" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="11">
         <v>2</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="13">
@@ -2118,14 +2124,14 @@
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="34"/>
+      <c r="A13" s="37"/>
       <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="11">
         <v>3</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="33" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="13">
@@ -2160,14 +2166,14 @@
       <c r="P13" s="13"/>
     </row>
     <row r="14" spans="1:16" ht="28">
-      <c r="A14" s="34"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="11">
         <v>4</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="32" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="13">
@@ -2192,14 +2198,14 @@
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="34"/>
+      <c r="A15" s="37"/>
       <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="11">
         <v>5</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="32" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="13">
@@ -2224,14 +2230,14 @@
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="34"/>
+      <c r="A16" s="37"/>
       <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="11">
         <v>6</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="32" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="13">
@@ -2256,14 +2262,14 @@
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="34"/>
+      <c r="A17" s="37"/>
       <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="11">
         <v>7</v>
       </c>
-      <c r="D17" s="42" t="s">
+      <c r="D17" s="32" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="13">
@@ -2298,14 +2304,14 @@
       <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="34"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="11">
         <v>8</v>
       </c>
-      <c r="D18" s="42" t="s">
+      <c r="D18" s="32" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="13">
@@ -2340,14 +2346,14 @@
       <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="34"/>
+      <c r="A19" s="37"/>
       <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="11">
         <v>9</v>
       </c>
-      <c r="D19" s="42"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="13">
         <v>6</v>
       </c>
@@ -2370,14 +2376,14 @@
       <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="34"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="30">
         <v>10</v>
       </c>
-      <c r="D20" s="43"/>
+      <c r="D20" s="33"/>
       <c r="E20" s="13">
         <v>6</v>
       </c>
@@ -2400,14 +2406,14 @@
       <c r="P20" s="13"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="35"/>
+      <c r="A21" s="38"/>
       <c r="B21" s="11" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="30">
         <v>11</v>
       </c>
-      <c r="D21" s="43"/>
+      <c r="D21" s="33"/>
       <c r="E21" s="13">
         <v>1</v>
       </c>
@@ -2439,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -2459,7 +2465,7 @@
     <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:19" ht="28">
       <c r="A1" s="21"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2507,8 +2513,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:19" ht="15" customHeight="1">
+      <c r="A2" s="39" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -2539,8 +2545,8 @@
       <c r="O2" s="22"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="37"/>
+    <row r="3" spans="1:19" ht="15" customHeight="1">
+      <c r="A3" s="40"/>
       <c r="B3" s="19" t="s">
         <v>11</v>
       </c>
@@ -2561,16 +2567,16 @@
         <v>15</v>
       </c>
       <c r="I3" s="31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" s="31">
         <v>5</v>
       </c>
       <c r="K3" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L3" s="31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M3" s="22">
         <v>45798</v>
@@ -2578,9 +2584,12 @@
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
       <c r="P3" s="21"/>
-    </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="37"/>
+      <c r="R3" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="40"/>
       <c r="B4" s="19" t="s">
         <v>11</v>
       </c>
@@ -2601,16 +2610,16 @@
         <v>18</v>
       </c>
       <c r="I4" s="31">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J4" s="31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K4" s="31">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L4" s="31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M4" s="22">
         <v>45798</v>
@@ -2618,9 +2627,12 @@
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
       <c r="P4" s="21"/>
-    </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="37"/>
+      <c r="S4" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1">
+      <c r="A5" s="40"/>
       <c r="B5" s="19" t="s">
         <v>11</v>
       </c>
@@ -2649,8 +2661,8 @@
       <c r="O5" s="22"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="38"/>
+    <row r="6" spans="1:19" ht="15" customHeight="1">
+      <c r="A6" s="41"/>
       <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
@@ -2758,7 +2770,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="42" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -2790,7 +2802,7 @@
       <c r="P2" s="25"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="40"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="24" t="s">
         <v>11</v>
       </c>
@@ -2811,16 +2823,16 @@
         <v>15</v>
       </c>
       <c r="I3" s="31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J3" s="31">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="31">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M3" s="27">
         <v>45798</v>
@@ -2830,7 +2842,7 @@
       <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="40"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
@@ -2851,16 +2863,16 @@
         <v>18</v>
       </c>
       <c r="I4" s="31">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" s="31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K4" s="31">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L4" s="31">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M4" s="27">
         <v>45798</v>
@@ -2870,7 +2882,7 @@
       <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="40"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -2900,7 +2912,7 @@
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="41"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="24" t="s">
         <v>11</v>
       </c>
@@ -2938,12 +2950,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3131,19 +3144,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3167,17 +3187,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A20CD7-940C-4B9D-96BC-D80893742B93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89C3E88-C7D7-4F1E-B1BD-684B743C033B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="1" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>MOD.</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>DAMAZ</t>
+  </si>
+  <si>
+    <t>Comparar colunas E com I, F com J, G com k, H com L. caso não tenham sido preenchidas as colunas I,J,K,L ainda é para desconsiderar. Caso a quantidade aumente ou diminua é para colocar. Quero um texo começando com um paragrafo fazendo a solicitação e abaixo separado por grupo (epf, dpf, ppf, pcf) as aulas M1.1, M1.2.... informando somente a solicitação de ajuste para mais ou para menos, caso não tenha ajuste não presida relacionar.</t>
   </si>
 </sst>
 </file>
@@ -252,7 +255,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -286,6 +289,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -470,6 +479,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,26 +848,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="5"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -903,8 +915,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:16" ht="28.5">
+      <c r="A2" s="36" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -938,7 +950,7 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="35"/>
+      <c r="A3" s="36"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -960,17 +972,27 @@
       <c r="H3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="I3" s="5">
+        <v>10</v>
+      </c>
+      <c r="J3" s="5">
+        <v>13</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>5</v>
+      </c>
+      <c r="M3" s="6">
+        <v>46169</v>
+      </c>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" ht="28">
-      <c r="A4" s="35"/>
+    <row r="4" spans="1:16" ht="28.5">
+      <c r="A4" s="36"/>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1011,8 +1033,8 @@
       <c r="O4" s="6"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="35"/>
+    <row r="5" spans="1:16">
+      <c r="A5" s="36"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1076,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="35"/>
+      <c r="A6" s="36"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
@@ -1096,7 +1118,7 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="35"/>
+      <c r="A7" s="36"/>
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
@@ -1138,7 +1160,7 @@
       <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="35"/>
+      <c r="A8" s="36"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
@@ -1180,7 +1202,7 @@
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="35"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1203,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1222,7 +1244,7 @@
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="35"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
@@ -1245,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J10" s="5">
         <v>0</v>
@@ -1264,7 +1286,7 @@
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="35"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1306,7 +1328,7 @@
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="35"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
@@ -1348,7 +1370,7 @@
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="35"/>
+      <c r="A13" s="36"/>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1390,7 +1412,7 @@
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="35"/>
+      <c r="A14" s="36"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
@@ -1432,7 +1454,7 @@
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="35"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
@@ -1464,7 +1486,7 @@
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="35"/>
+      <c r="A16" s="36"/>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -1496,7 +1518,7 @@
       <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="35"/>
+      <c r="A17" s="36"/>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
@@ -1537,8 +1559,8 @@
       <c r="O17" s="6"/>
       <c r="P17" s="5"/>
     </row>
-    <row r="18" spans="1:16" ht="28">
-      <c r="A18" s="35"/>
+    <row r="18" spans="1:16" ht="28.5">
+      <c r="A18" s="36"/>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
@@ -1570,7 +1592,7 @@
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="35"/>
+      <c r="A19" s="36"/>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
@@ -1612,26 +1634,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="13"/>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -1679,8 +1701,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:16" ht="28.5">
+      <c r="A2" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -1704,17 +1726,27 @@
       <c r="H2" s="13">
         <v>0</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
+      <c r="I2" s="13">
+        <v>16</v>
+      </c>
+      <c r="J2" s="13">
+        <v>6</v>
+      </c>
+      <c r="K2" s="13">
+        <v>0</v>
+      </c>
+      <c r="L2" s="13">
+        <v>0</v>
+      </c>
+      <c r="M2" s="14">
+        <v>46170</v>
+      </c>
       <c r="N2" s="14"/>
       <c r="O2" s="14"/>
       <c r="P2" s="13"/>
     </row>
-    <row r="3" spans="1:16" ht="28">
-      <c r="A3" s="37"/>
+    <row r="3" spans="1:16" ht="28.5">
+      <c r="A3" s="38"/>
       <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
@@ -1736,17 +1768,27 @@
       <c r="H3" s="13">
         <v>4</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
+      <c r="I3" s="13">
+        <v>25</v>
+      </c>
+      <c r="J3" s="13">
+        <v>9</v>
+      </c>
+      <c r="K3" s="13">
+        <v>0</v>
+      </c>
+      <c r="L3" s="13">
+        <v>4</v>
+      </c>
+      <c r="M3" s="14">
+        <v>46170</v>
+      </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14"/>
       <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="37"/>
+      <c r="A4" s="38"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
@@ -1787,8 +1829,8 @@
       <c r="O4" s="14"/>
       <c r="P4" s="13"/>
     </row>
-    <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="37"/>
+    <row r="5" spans="1:16">
+      <c r="A5" s="38"/>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
@@ -1829,8 +1871,8 @@
       <c r="O5" s="14"/>
       <c r="P5" s="13"/>
     </row>
-    <row r="6" spans="1:16" ht="28">
-      <c r="A6" s="37"/>
+    <row r="6" spans="1:16" ht="28.5">
+      <c r="A6" s="38"/>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
@@ -1872,7 +1914,7 @@
       <c r="P6" s="16"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="37"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
@@ -1914,7 +1956,7 @@
       <c r="P7" s="17"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="37"/>
+      <c r="A8" s="38"/>
       <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
@@ -1956,7 +1998,7 @@
       <c r="P8" s="13"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="37"/>
+      <c r="A9" s="38"/>
       <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
@@ -1998,7 +2040,7 @@
       <c r="P9" s="13"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="37"/>
+      <c r="A10" s="38"/>
       <c r="B10" s="11" t="s">
         <v>11</v>
       </c>
@@ -2040,7 +2082,7 @@
       <c r="P10" s="13"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="37"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
@@ -2082,7 +2124,7 @@
       <c r="P11" s="18"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="37"/>
+      <c r="A12" s="38"/>
       <c r="B12" s="11" t="s">
         <v>12</v>
       </c>
@@ -2124,7 +2166,7 @@
       <c r="P12" s="13"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="37"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="11" t="s">
         <v>12</v>
       </c>
@@ -2165,8 +2207,8 @@
       <c r="O13" s="14"/>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" spans="1:16" ht="28">
-      <c r="A14" s="37"/>
+    <row r="14" spans="1:16" ht="28.5">
+      <c r="A14" s="38"/>
       <c r="B14" s="11" t="s">
         <v>12</v>
       </c>
@@ -2198,7 +2240,7 @@
       <c r="P14" s="13"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="37"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
@@ -2230,7 +2272,7 @@
       <c r="P15" s="13"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="37"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
@@ -2262,7 +2304,7 @@
       <c r="P16" s="13"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="37"/>
+      <c r="A17" s="38"/>
       <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
@@ -2304,7 +2346,7 @@
       <c r="P17" s="13"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="37"/>
+      <c r="A18" s="38"/>
       <c r="B18" s="11" t="s">
         <v>12</v>
       </c>
@@ -2346,7 +2388,7 @@
       <c r="P18" s="13"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="37"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
@@ -2376,7 +2418,7 @@
       <c r="P19" s="13"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="37"/>
+      <c r="A20" s="38"/>
       <c r="B20" s="11" t="s">
         <v>12</v>
       </c>
@@ -2406,7 +2448,7 @@
       <c r="P20" s="13"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="38"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="11" t="s">
         <v>12</v>
       </c>
@@ -2446,26 +2488,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="28">
+    <row r="1" spans="1:19" ht="30">
       <c r="A1" s="21"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -2514,7 +2556,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="40" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="19" t="s">
@@ -2546,7 +2588,7 @@
       <c r="P2" s="21"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="40"/>
+      <c r="A3" s="41"/>
       <c r="B3" s="19" t="s">
         <v>11</v>
       </c>
@@ -2566,16 +2608,16 @@
       <c r="H3" s="21">
         <v>15</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="35">
         <v>7</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="35">
         <v>5</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="35">
         <v>10</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="35">
         <v>11</v>
       </c>
       <c r="M3" s="22">
@@ -2589,7 +2631,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="40"/>
+      <c r="A4" s="41"/>
       <c r="B4" s="19" t="s">
         <v>11</v>
       </c>
@@ -2609,16 +2651,16 @@
       <c r="H4" s="21">
         <v>18</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="35">
         <v>6</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="35">
         <v>6</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="35">
         <v>6</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="35">
         <v>10</v>
       </c>
       <c r="M4" s="22">
@@ -2632,7 +2674,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="40"/>
+      <c r="A5" s="41"/>
       <c r="B5" s="19" t="s">
         <v>11</v>
       </c>
@@ -2662,7 +2704,7 @@
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="41"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="19" t="s">
         <v>11</v>
       </c>
@@ -2701,27 +2743,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
+    <row r="1" spans="1:16" ht="30">
       <c r="A1" s="26"/>
       <c r="B1" s="24" t="s">
         <v>0</v>
@@ -2770,7 +2812,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="24" t="s">
@@ -2802,7 +2844,7 @@
       <c r="P2" s="25"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="43"/>
+      <c r="A3" s="44"/>
       <c r="B3" s="24" t="s">
         <v>11</v>
       </c>
@@ -2842,7 +2884,7 @@
       <c r="P3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="43"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="24" t="s">
         <v>11</v>
       </c>
@@ -2882,7 +2924,7 @@
       <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="43"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
       </c>
@@ -2912,7 +2954,7 @@
       <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="44"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="24" t="s">
         <v>11</v>
       </c>
@@ -2940,6 +2982,11 @@
       <c r="N6" s="27"/>
       <c r="O6" s="27"/>
       <c r="P6" s="26"/>
+    </row>
+    <row r="12" spans="1:16" ht="409.5">
+      <c r="F12" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2950,6 +2997,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
@@ -2959,7 +3015,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010074A154D0DC1E2447ADD5D8CA556ECA80" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a1fb4aabcd5adab87d9e1296b6f2d38">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22554d0a-1932-447e-b007-a2186b2152bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00325a2f7f39d3ee3bb3596f142ab400" ns2:_="">
     <xsd:import namespace="22554d0a-1932-447e-b007-a2186b2152bd"/>
@@ -3143,16 +3199,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -3168,7 +3223,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3186,14 +3241,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" enabled="0" method="" siteId="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" removed="1"/>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89C3E88-C7D7-4F1E-B1BD-684B743C033B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B6356-A8F5-47A6-87F6-8136181AD4CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="1" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -940,10 +940,18 @@
       <c r="H2" s="5">
         <v>0</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="I2" s="5">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5">
+        <v>2</v>
+      </c>
+      <c r="K2" s="5">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
       <c r="M2" s="5"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
@@ -2997,25 +3005,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010074A154D0DC1E2447ADD5D8CA556ECA80" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a1fb4aabcd5adab87d9e1296b6f2d38">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22554d0a-1932-447e-b007-a2186b2152bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00325a2f7f39d3ee3bb3596f142ab400" ns2:_="">
     <xsd:import namespace="22554d0a-1932-447e-b007-a2186b2152bd"/>
@@ -3199,10 +3188,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3224,19 +3242,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9B6356-A8F5-47A6-87F6-8136181AD4CB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34978D2C-8681-4986-AF56-C7E3C14E4EB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
@@ -264,12 +264,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -295,6 +289,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -423,15 +423,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -447,71 +438,86 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,766 +874,768 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30">
-      <c r="A1" s="5"/>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="35"/>
+      <c r="B1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="33" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="28.5">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="35">
         <v>9</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="35">
         <v>9</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G2" s="35">
+        <v>0</v>
+      </c>
+      <c r="H2" s="35">
+        <v>0</v>
+      </c>
+      <c r="I2" s="35">
         <v>18</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="35">
         <v>2</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="35">
         <v>14</v>
       </c>
-      <c r="L2" s="5">
-        <v>0</v>
-      </c>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="5"/>
+      <c r="L2" s="35">
+        <v>0</v>
+      </c>
+      <c r="M2" s="40">
+        <v>46170</v>
+      </c>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="35"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="36"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="35">
         <v>9</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="35">
         <v>9</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="35">
+        <v>0</v>
+      </c>
+      <c r="H3" s="35">
         <v>4</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="35">
         <v>10</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="35">
         <v>13</v>
       </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="K3" s="35">
+        <v>0</v>
+      </c>
+      <c r="L3" s="35">
         <v>5</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="40">
         <v>46169</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="4"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="41"/>
     </row>
     <row r="4" spans="1:16" ht="28.5">
-      <c r="A4" s="36"/>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="A4" s="39"/>
+      <c r="B4" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="33">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="35">
         <v>13</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="35">
+        <v>0</v>
+      </c>
+      <c r="G4" s="35">
         <v>15</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="35">
         <v>15</v>
       </c>
-      <c r="I4" s="31">
-        <v>8</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="I4" s="35">
+        <v>8</v>
+      </c>
+      <c r="J4" s="35">
         <v>5</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="35">
         <v>15</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="35">
         <v>10</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="40">
         <v>45798</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="5"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="35"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="36"/>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="A5" s="39"/>
+      <c r="B5" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="33">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="37">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="35">
         <v>2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="35">
         <v>17</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="35">
         <v>20</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="35">
         <v>12</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="35">
         <v>1</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="35">
         <v>17</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="35">
         <v>15</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="40">
         <v>45798</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="5"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="35"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="36"/>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="A6" s="39"/>
+      <c r="B6" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="33">
         <v>3</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="35">
         <v>10</v>
       </c>
-      <c r="F6" s="5">
-        <v>8</v>
-      </c>
-      <c r="G6" s="5">
-        <v>8</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="F6" s="35">
+        <v>8</v>
+      </c>
+      <c r="G6" s="35">
+        <v>8</v>
+      </c>
+      <c r="H6" s="35">
         <v>15</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="35">
         <v>10</v>
       </c>
-      <c r="J6" s="5">
-        <v>8</v>
-      </c>
-      <c r="K6" s="31">
+      <c r="J6" s="35">
+        <v>8</v>
+      </c>
+      <c r="K6" s="35">
         <v>16</v>
       </c>
-      <c r="L6" s="31">
-        <v>8</v>
-      </c>
-      <c r="M6" s="6">
+      <c r="L6" s="35">
+        <v>8</v>
+      </c>
+      <c r="M6" s="40">
         <v>45798</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="8"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="42"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="36"/>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="A7" s="39"/>
+      <c r="B7" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="33">
         <v>4</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="35">
         <v>13</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="35">
+        <v>0</v>
+      </c>
+      <c r="G7" s="35">
         <v>10</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="35">
         <v>18</v>
       </c>
-      <c r="I7" s="31">
-        <v>8</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="I7" s="35">
+        <v>8</v>
+      </c>
+      <c r="J7" s="35">
         <v>10</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="35">
         <v>10</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="35">
         <v>16</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="40">
         <v>45798</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="43"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="36"/>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="A8" s="39"/>
+      <c r="B8" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="33">
         <v>5</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="5">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5">
-        <v>8</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="E8" s="35">
+        <v>11</v>
+      </c>
+      <c r="F8" s="35">
+        <v>8</v>
+      </c>
+      <c r="G8" s="35">
         <v>24</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="35">
         <v>23</v>
       </c>
-      <c r="I8" s="5">
-        <v>11</v>
-      </c>
-      <c r="J8" s="5">
-        <v>8</v>
-      </c>
-      <c r="K8" s="5">
+      <c r="I8" s="35">
+        <v>11</v>
+      </c>
+      <c r="J8" s="35">
+        <v>8</v>
+      </c>
+      <c r="K8" s="35">
         <v>24</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="35">
         <v>21</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="40">
         <v>45799</v>
       </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="5"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="35"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="36"/>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="A9" s="39"/>
+      <c r="B9" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="33">
         <v>6</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="35">
         <v>10</v>
       </c>
-      <c r="F9" s="5">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
-        <v>8</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="F9" s="35">
+        <v>0</v>
+      </c>
+      <c r="G9" s="38">
+        <v>8</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="35">
         <v>12</v>
       </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>8</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="J9" s="35">
+        <v>0</v>
+      </c>
+      <c r="K9" s="35">
+        <v>8</v>
+      </c>
+      <c r="L9" s="35">
+        <v>0</v>
+      </c>
+      <c r="M9" s="40">
         <v>45799</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="5"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="35"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="36"/>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="33">
         <v>7</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="35">
         <v>5</v>
       </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="29">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
-        <v>11</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="F10" s="35">
+        <v>0</v>
+      </c>
+      <c r="G10" s="38">
+        <v>0</v>
+      </c>
+      <c r="H10" s="35">
+        <v>0</v>
+      </c>
+      <c r="I10" s="35">
+        <v>11</v>
+      </c>
+      <c r="J10" s="35">
+        <v>0</v>
+      </c>
+      <c r="K10" s="35">
+        <v>0</v>
+      </c>
+      <c r="L10" s="35">
+        <v>0</v>
+      </c>
+      <c r="M10" s="40">
         <v>45799</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="5"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="35"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="36"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="39"/>
+      <c r="B11" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="33">
         <v>1</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="35">
+        <v>11</v>
+      </c>
+      <c r="F11" s="35">
         <v>2</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>11</v>
-      </c>
-      <c r="J11" s="5">
+      <c r="G11" s="35">
+        <v>0</v>
+      </c>
+      <c r="H11" s="35">
+        <v>0</v>
+      </c>
+      <c r="I11" s="35">
+        <v>11</v>
+      </c>
+      <c r="J11" s="35">
         <v>1</v>
       </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="K11" s="35">
+        <v>0</v>
+      </c>
+      <c r="L11" s="35">
+        <v>0</v>
+      </c>
+      <c r="M11" s="40">
         <v>45799</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="10"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="44"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="36"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="39"/>
+      <c r="B12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="33">
         <v>2</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="35">
         <v>2</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="35">
         <v>4</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="G12" s="35">
+        <v>0</v>
+      </c>
+      <c r="H12" s="35">
+        <v>0</v>
+      </c>
+      <c r="I12" s="35">
         <v>2</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="35">
         <v>4</v>
       </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="K12" s="35">
+        <v>0</v>
+      </c>
+      <c r="L12" s="35">
+        <v>0</v>
+      </c>
+      <c r="M12" s="40">
         <v>45798</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="5"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="35"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="36"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="39"/>
+      <c r="B13" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="33">
         <v>3</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="35">
         <v>16</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="38">
         <v>14</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="35">
         <v>4</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="35">
         <v>24</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="35">
         <v>16</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="35">
         <v>14</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="35">
         <v>4</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="35">
         <v>20</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="40">
         <v>45798</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="5"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="35"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="36"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="39"/>
+      <c r="B14" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="33">
         <v>4</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="35">
         <v>2</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="F14" s="35">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35">
+        <v>0</v>
+      </c>
+      <c r="H14" s="35">
+        <v>0</v>
+      </c>
+      <c r="I14" s="35">
         <v>2</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="35">
         <v>4</v>
       </c>
-      <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
+      <c r="K14" s="35">
+        <v>0</v>
+      </c>
+      <c r="L14" s="35">
+        <v>0</v>
+      </c>
+      <c r="M14" s="40">
         <v>45798</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="5"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="35"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="36"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="39"/>
+      <c r="B15" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="33">
         <v>5</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="35">
         <v>5</v>
       </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="5"/>
+      <c r="F15" s="35">
+        <v>0</v>
+      </c>
+      <c r="G15" s="35">
+        <v>0</v>
+      </c>
+      <c r="H15" s="35">
+        <v>0</v>
+      </c>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="35"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="36"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="39"/>
+      <c r="B16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="33">
         <v>6</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="35">
         <v>4</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="35">
         <v>4</v>
       </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="5"/>
+      <c r="G16" s="35">
+        <v>0</v>
+      </c>
+      <c r="H16" s="35">
+        <v>0</v>
+      </c>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="35"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="36"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="39"/>
+      <c r="B17" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="33">
         <v>7</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="35">
         <v>10</v>
       </c>
-      <c r="F17" s="5">
-        <v>8</v>
-      </c>
-      <c r="G17" s="5">
-        <v>8</v>
-      </c>
-      <c r="H17" s="5">
+      <c r="F17" s="35">
+        <v>8</v>
+      </c>
+      <c r="G17" s="35">
+        <v>8</v>
+      </c>
+      <c r="H17" s="35">
         <v>20</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="35">
         <v>10</v>
       </c>
-      <c r="J17" s="5">
-        <v>8</v>
-      </c>
-      <c r="K17" s="31">
+      <c r="J17" s="35">
+        <v>8</v>
+      </c>
+      <c r="K17" s="35">
         <v>10</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="35">
         <v>13</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="40">
         <v>45798</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="5"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="35"/>
     </row>
     <row r="18" spans="1:16" ht="28.5">
-      <c r="A18" s="36"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="39"/>
+      <c r="B18" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="3">
-        <v>8</v>
-      </c>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="33">
+        <v>8</v>
+      </c>
+      <c r="D18" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="35">
         <v>9</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="35">
         <v>2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="35">
         <v>2</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="35">
         <v>2</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="5"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="35"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="36"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="33">
         <v>9</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="5">
+      <c r="D19" s="36"/>
+      <c r="E19" s="35">
         <v>6</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="35">
         <v>6</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="35">
         <v>2</v>
       </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
+      <c r="H19" s="35">
+        <v>0</v>
+      </c>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1662,828 +1670,828 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30">
-      <c r="A1" s="13"/>
-      <c r="B1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="5"/>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="28.5">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="5">
         <v>9</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="5">
         <v>9</v>
       </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="13">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
         <v>16</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="5">
         <v>6</v>
       </c>
-      <c r="K2" s="13">
-        <v>0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>0</v>
-      </c>
-      <c r="M2" s="14">
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
         <v>46170</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="13"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" ht="28.5">
-      <c r="A3" s="38"/>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="5">
         <v>15</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="5">
         <v>5</v>
       </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="5">
         <v>25</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="5">
         <v>9</v>
       </c>
-      <c r="K3" s="13">
-        <v>0</v>
-      </c>
-      <c r="L3" s="13">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
         <v>4</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="6">
         <v>46170</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="12"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="38"/>
-      <c r="B4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11">
+      <c r="A4" s="25"/>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="5">
         <v>12</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="5">
         <v>17</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="5">
         <v>20</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="5">
         <v>17</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="5">
         <v>15</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="6">
         <v>45798</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="13"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="38"/>
-      <c r="B5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="A5" s="25"/>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="7">
         <v>6</v>
       </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13">
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
         <v>6</v>
       </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
         <v>45798</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="13"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="28.5">
-      <c r="A6" s="38"/>
-      <c r="B6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="A6" s="25"/>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="5">
         <v>10</v>
       </c>
-      <c r="F6" s="13">
-        <v>8</v>
-      </c>
-      <c r="G6" s="13">
-        <v>8</v>
-      </c>
-      <c r="H6" s="13">
+      <c r="F6" s="5">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5">
         <v>15</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="13">
-        <v>8</v>
-      </c>
-      <c r="K6" s="31">
+      <c r="J6" s="5">
+        <v>8</v>
+      </c>
+      <c r="K6" s="5">
         <v>16</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="5">
         <v>18</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="6">
         <v>45798</v>
       </c>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="16"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="38"/>
-      <c r="B7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="A7" s="25"/>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="5">
         <v>13</v>
       </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
         <v>10</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="5">
         <v>18</v>
       </c>
-      <c r="I7" s="31">
-        <v>8</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="I7" s="5">
+        <v>8</v>
+      </c>
+      <c r="J7" s="5">
         <v>10</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="5">
         <v>10</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="5">
         <v>16</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="6">
         <v>45798</v>
       </c>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="17"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="38"/>
-      <c r="B8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="A8" s="25"/>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="5">
         <v>6</v>
       </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="31">
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <v>5</v>
       </c>
-      <c r="J8" s="13">
-        <v>0</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="14">
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
         <v>45798</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="13"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="38"/>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="A9" s="25"/>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="13">
-        <v>11</v>
-      </c>
-      <c r="F9" s="13">
-        <v>8</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="E9" s="5">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
         <v>24</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="5">
         <v>23</v>
       </c>
-      <c r="I9" s="13">
-        <v>11</v>
-      </c>
-      <c r="J9" s="13">
-        <v>8</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="I9" s="5">
+        <v>11</v>
+      </c>
+      <c r="J9" s="5">
+        <v>8</v>
+      </c>
+      <c r="K9" s="5">
         <v>24</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="5">
         <v>21</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="6">
         <v>45798</v>
       </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="13"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="38"/>
-      <c r="B10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="A10" s="25"/>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="5">
         <v>10</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31">
-        <v>11</v>
-      </c>
-      <c r="J10" s="31">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>11</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
         <v>45798</v>
       </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="13"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="38"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="13">
-        <v>11</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="5">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5">
         <v>2</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
-        <v>11</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>11</v>
+      </c>
+      <c r="J11" s="5">
         <v>1</v>
       </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14">
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <v>45799</v>
       </c>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="18"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="38"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="5">
         <v>2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="5">
         <v>4</v>
       </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
         <v>2</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="5">
         <v>4</v>
       </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="14">
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
         <v>45798</v>
       </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="13"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="38"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="5">
         <v>16</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="5">
         <v>14</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="5">
         <v>4</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="5">
         <v>24</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="5">
         <v>16</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="5">
         <v>14</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="5">
         <v>4</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="5">
         <v>20</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="6">
         <v>45798</v>
       </c>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="13"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16" ht="28.5">
-      <c r="A14" s="38"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="5">
         <v>6</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="5">
         <v>2</v>
       </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="13"/>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="38"/>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="3">
         <v>5</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="13">
-        <v>8</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="13"/>
+      <c r="E15" s="5">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="38"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="13">
-        <v>8</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="E16" s="5">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5">
         <v>2</v>
       </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="13"/>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="38"/>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="3">
         <v>7</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="5">
         <v>2</v>
       </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="31">
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
         <v>5</v>
       </c>
-      <c r="J17" s="13">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="14">
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
         <v>45798</v>
       </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="13"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="38"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="11">
-        <v>8</v>
-      </c>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="3">
+        <v>8</v>
+      </c>
+      <c r="D18" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="5">
         <v>10</v>
       </c>
-      <c r="F18" s="13">
-        <v>8</v>
-      </c>
-      <c r="G18" s="13">
-        <v>8</v>
-      </c>
-      <c r="H18" s="13">
+      <c r="F18" s="5">
+        <v>8</v>
+      </c>
+      <c r="G18" s="5">
+        <v>8</v>
+      </c>
+      <c r="H18" s="5">
         <v>20</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="5">
         <v>10</v>
       </c>
-      <c r="J18" s="13">
-        <v>8</v>
-      </c>
-      <c r="K18" s="31">
+      <c r="J18" s="5">
+        <v>8</v>
+      </c>
+      <c r="K18" s="5">
         <v>10</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="5">
         <v>13</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="6">
         <v>45798</v>
       </c>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="13"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="38"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="13">
+      <c r="D19" s="45"/>
+      <c r="E19" s="5">
         <v>6</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="5">
         <v>2</v>
       </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="13"/>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="5"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="38"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="21">
         <v>10</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="13">
+      <c r="D20" s="46"/>
+      <c r="E20" s="5">
         <v>6</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="5">
         <v>6</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="5">
         <v>2</v>
       </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="39"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="30">
-        <v>11</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="13">
+      <c r="C21" s="21">
+        <v>11</v>
+      </c>
+      <c r="D21" s="46"/>
+      <c r="E21" s="5">
         <v>1</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="5">
         <v>4</v>
       </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2516,230 +2524,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30">
-      <c r="A1" s="21"/>
-      <c r="B1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="19" t="s">
+      <c r="A1" s="13"/>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21">
+      <c r="D2" s="12"/>
+      <c r="E2" s="13">
         <v>14</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="13">
         <v>6</v>
       </c>
-      <c r="G2" s="21">
-        <v>0</v>
-      </c>
-      <c r="H2" s="21">
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13">
         <v>15</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="21"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="19">
+      <c r="A3" s="28"/>
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21">
+      <c r="D3" s="12"/>
+      <c r="E3" s="13">
         <v>10</v>
       </c>
-      <c r="F3" s="21">
-        <v>8</v>
-      </c>
-      <c r="G3" s="21">
-        <v>8</v>
-      </c>
-      <c r="H3" s="21">
+      <c r="F3" s="13">
+        <v>8</v>
+      </c>
+      <c r="G3" s="13">
+        <v>8</v>
+      </c>
+      <c r="H3" s="13">
         <v>15</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="23">
         <v>7</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="23">
         <v>5</v>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="23">
         <v>10</v>
       </c>
-      <c r="L3" s="35">
-        <v>11</v>
-      </c>
-      <c r="M3" s="22">
+      <c r="L3" s="23">
+        <v>11</v>
+      </c>
+      <c r="M3" s="14">
         <v>45798</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="21"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="13"/>
       <c r="R3" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="41"/>
-      <c r="B4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="A4" s="28"/>
+      <c r="B4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="11">
         <v>2</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="23">
+      <c r="D4" s="12"/>
+      <c r="E4" s="15">
         <v>13</v>
       </c>
-      <c r="F4" s="21">
-        <v>0</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
         <v>10</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="13">
         <v>18</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="23">
         <v>6</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="23">
         <v>6</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="23">
         <v>6</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="23">
         <v>10</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="14">
         <v>45798</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="21"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="13"/>
       <c r="S4" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="41"/>
-      <c r="B5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="A5" s="28"/>
+      <c r="B5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
         <v>5</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21">
-        <v>11</v>
-      </c>
-      <c r="F5" s="21">
-        <v>8</v>
-      </c>
-      <c r="G5" s="21">
+      <c r="D5" s="12"/>
+      <c r="E5" s="13">
+        <v>11</v>
+      </c>
+      <c r="F5" s="13">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13">
         <v>24</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="13">
         <v>23</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="42"/>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="19">
+      <c r="A6" s="29"/>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="11">
         <v>6</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21">
+      <c r="D6" s="12"/>
+      <c r="E6" s="13">
         <v>2</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="13">
         <v>4</v>
       </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2772,224 +2780,224 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30">
-      <c r="A1" s="26"/>
-      <c r="B1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="24" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26">
+      <c r="D2" s="17"/>
+      <c r="E2" s="18">
         <v>14</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="18">
         <v>6</v>
       </c>
-      <c r="G2" s="26">
-        <v>0</v>
-      </c>
-      <c r="H2" s="26">
+      <c r="G2" s="18">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18">
         <v>15</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="25"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="17"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="44"/>
-      <c r="B3" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="24">
+      <c r="A3" s="31"/>
+      <c r="B3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="16">
         <v>1</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26">
+      <c r="D3" s="17"/>
+      <c r="E3" s="18">
         <v>10</v>
       </c>
-      <c r="F3" s="26">
-        <v>8</v>
-      </c>
-      <c r="G3" s="26">
-        <v>8</v>
-      </c>
-      <c r="H3" s="26">
+      <c r="F3" s="18">
+        <v>8</v>
+      </c>
+      <c r="G3" s="18">
+        <v>8</v>
+      </c>
+      <c r="H3" s="18">
         <v>15</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="22">
         <v>10</v>
       </c>
-      <c r="J3" s="31">
-        <v>8</v>
-      </c>
-      <c r="K3" s="31">
+      <c r="J3" s="22">
+        <v>8</v>
+      </c>
+      <c r="K3" s="22">
         <v>16</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="22">
         <v>18</v>
       </c>
-      <c r="M3" s="27">
+      <c r="M3" s="19">
         <v>45798</v>
       </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="26"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="44"/>
-      <c r="B4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="A4" s="31"/>
+      <c r="B4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="16">
         <v>2</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="28">
+      <c r="D4" s="17"/>
+      <c r="E4" s="20">
         <v>13</v>
       </c>
-      <c r="F4" s="26">
-        <v>0</v>
-      </c>
-      <c r="G4" s="26">
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
         <v>10</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="18">
         <v>18</v>
       </c>
-      <c r="I4" s="31">
-        <v>8</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="I4" s="22">
+        <v>8</v>
+      </c>
+      <c r="J4" s="22">
         <v>10</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="22">
         <v>10</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="22">
         <v>16</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="19">
         <v>45798</v>
       </c>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="26"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="A5" s="31"/>
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16">
         <v>5</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="26">
-        <v>11</v>
-      </c>
-      <c r="F5" s="26">
-        <v>8</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="D5" s="17"/>
+      <c r="E5" s="18">
+        <v>11</v>
+      </c>
+      <c r="F5" s="18">
+        <v>8</v>
+      </c>
+      <c r="G5" s="18">
         <v>24</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="18">
         <v>23</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="26"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="18"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="45"/>
-      <c r="B6" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="A6" s="32"/>
+      <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="16">
         <v>6</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26">
+      <c r="D6" s="17"/>
+      <c r="E6" s="18">
         <v>2</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="18">
         <v>4</v>
       </c>
-      <c r="G6" s="26">
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>0</v>
-      </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="26"/>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="18"/>
     </row>
     <row r="12" spans="1:16" ht="409.5">
       <c r="F12" s="1" t="s">

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34978D2C-8681-4986-AF56-C7E3C14E4EB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BBB7B5-6822-4C1F-9098-2794F6D020F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -447,33 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -492,9 +465,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -518,6 +488,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,768 +874,768 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30">
-      <c r="A1" s="35"/>
-      <c r="B1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="33" t="s">
+      <c r="A1" s="26"/>
+      <c r="B1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="D1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="33" t="s">
+      <c r="G1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="H1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="33" t="s">
+      <c r="P1" s="24" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="28.5">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="35">
+      <c r="E2" s="26">
         <v>9</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="26">
         <v>9</v>
       </c>
-      <c r="G2" s="35">
-        <v>0</v>
-      </c>
-      <c r="H2" s="35">
-        <v>0</v>
-      </c>
-      <c r="I2" s="35">
+      <c r="G2" s="26">
+        <v>0</v>
+      </c>
+      <c r="H2" s="26">
+        <v>0</v>
+      </c>
+      <c r="I2" s="26">
         <v>18</v>
       </c>
-      <c r="J2" s="35">
+      <c r="J2" s="26">
         <v>2</v>
       </c>
-      <c r="K2" s="35">
+      <c r="K2" s="26">
         <v>14</v>
       </c>
-      <c r="L2" s="35">
-        <v>0</v>
-      </c>
-      <c r="M2" s="40">
+      <c r="L2" s="26">
+        <v>0</v>
+      </c>
+      <c r="M2" s="30">
         <v>46170</v>
       </c>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="35"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="39"/>
-      <c r="B3" s="33" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="35">
+      <c r="E3" s="26">
         <v>9</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="26">
         <v>9</v>
       </c>
-      <c r="G3" s="35">
-        <v>0</v>
-      </c>
-      <c r="H3" s="35">
+      <c r="G3" s="26">
+        <v>0</v>
+      </c>
+      <c r="H3" s="26">
         <v>4</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="26">
         <v>10</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="26">
         <v>13</v>
       </c>
-      <c r="K3" s="35">
-        <v>0</v>
-      </c>
-      <c r="L3" s="35">
+      <c r="K3" s="26">
+        <v>0</v>
+      </c>
+      <c r="L3" s="26">
         <v>5</v>
       </c>
-      <c r="M3" s="40">
+      <c r="M3" s="30">
         <v>46169</v>
       </c>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="41"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="31"/>
     </row>
     <row r="4" spans="1:16" ht="28.5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="33">
+      <c r="A4" s="38"/>
+      <c r="B4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="24">
         <v>1</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="26">
         <v>13</v>
       </c>
-      <c r="F4" s="35">
-        <v>0</v>
-      </c>
-      <c r="G4" s="35">
+      <c r="F4" s="26">
+        <v>0</v>
+      </c>
+      <c r="G4" s="26">
         <v>15</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="26">
         <v>15</v>
       </c>
-      <c r="I4" s="35">
-        <v>8</v>
-      </c>
-      <c r="J4" s="35">
+      <c r="I4" s="26">
+        <v>8</v>
+      </c>
+      <c r="J4" s="26">
         <v>5</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="26">
         <v>15</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="26">
         <v>10</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="30">
         <v>45798</v>
       </c>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="35"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="26"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="39"/>
-      <c r="B5" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="33">
+      <c r="A5" s="38"/>
+      <c r="B5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="24">
         <v>2</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="28">
         <v>12</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="26">
         <v>2</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="26">
         <v>17</v>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="26">
         <v>20</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="26">
         <v>12</v>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="26">
         <v>1</v>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="26">
         <v>17</v>
       </c>
-      <c r="L5" s="35">
+      <c r="L5" s="26">
         <v>15</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="30">
         <v>45798</v>
       </c>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="35"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="39"/>
-      <c r="B6" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="33">
+      <c r="A6" s="38"/>
+      <c r="B6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="26">
         <v>10</v>
       </c>
-      <c r="F6" s="35">
-        <v>8</v>
-      </c>
-      <c r="G6" s="35">
-        <v>8</v>
-      </c>
-      <c r="H6" s="35">
+      <c r="F6" s="26">
+        <v>8</v>
+      </c>
+      <c r="G6" s="26">
+        <v>8</v>
+      </c>
+      <c r="H6" s="26">
         <v>15</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="26">
         <v>10</v>
       </c>
-      <c r="J6" s="35">
-        <v>8</v>
-      </c>
-      <c r="K6" s="35">
+      <c r="J6" s="26">
+        <v>8</v>
+      </c>
+      <c r="K6" s="26">
         <v>16</v>
       </c>
-      <c r="L6" s="35">
-        <v>8</v>
-      </c>
-      <c r="M6" s="40">
+      <c r="L6" s="26">
+        <v>8</v>
+      </c>
+      <c r="M6" s="30">
         <v>45798</v>
       </c>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="42"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="32"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="39"/>
-      <c r="B7" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="33">
+      <c r="A7" s="38"/>
+      <c r="B7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="24">
         <v>4</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="26">
         <v>13</v>
       </c>
-      <c r="F7" s="35">
-        <v>0</v>
-      </c>
-      <c r="G7" s="35">
+      <c r="F7" s="26">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26">
         <v>10</v>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="26">
         <v>18</v>
       </c>
-      <c r="I7" s="35">
-        <v>8</v>
-      </c>
-      <c r="J7" s="35">
+      <c r="I7" s="26">
+        <v>8</v>
+      </c>
+      <c r="J7" s="26">
         <v>10</v>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="26">
         <v>10</v>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="26">
         <v>16</v>
       </c>
-      <c r="M7" s="40">
+      <c r="M7" s="30">
         <v>45798</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="43"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="33"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="39"/>
-      <c r="B8" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="33">
+      <c r="A8" s="38"/>
+      <c r="B8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="24">
         <v>5</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="35">
-        <v>11</v>
-      </c>
-      <c r="F8" s="35">
-        <v>8</v>
-      </c>
-      <c r="G8" s="35">
+      <c r="E8" s="26">
+        <v>11</v>
+      </c>
+      <c r="F8" s="26">
+        <v>8</v>
+      </c>
+      <c r="G8" s="26">
         <v>24</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="26">
         <v>23</v>
       </c>
-      <c r="I8" s="35">
-        <v>11</v>
-      </c>
-      <c r="J8" s="35">
-        <v>8</v>
-      </c>
-      <c r="K8" s="35">
+      <c r="I8" s="26">
+        <v>11</v>
+      </c>
+      <c r="J8" s="26">
+        <v>8</v>
+      </c>
+      <c r="K8" s="26">
         <v>24</v>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="26">
         <v>21</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M8" s="30">
         <v>45799</v>
       </c>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="35"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="26"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="39"/>
-      <c r="B9" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="33">
+      <c r="A9" s="38"/>
+      <c r="B9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="24">
         <v>6</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="26">
         <v>10</v>
       </c>
-      <c r="F9" s="35">
-        <v>0</v>
-      </c>
-      <c r="G9" s="38">
-        <v>8</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
-      </c>
-      <c r="I9" s="35">
+      <c r="F9" s="26">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29">
+        <v>8</v>
+      </c>
+      <c r="H9" s="26">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26">
         <v>12</v>
       </c>
-      <c r="J9" s="35">
-        <v>0</v>
-      </c>
-      <c r="K9" s="35">
-        <v>8</v>
-      </c>
-      <c r="L9" s="35">
-        <v>0</v>
-      </c>
-      <c r="M9" s="40">
+      <c r="J9" s="26">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26">
+        <v>8</v>
+      </c>
+      <c r="L9" s="26">
+        <v>0</v>
+      </c>
+      <c r="M9" s="30">
         <v>45799</v>
       </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="35"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="39"/>
-      <c r="B10" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="33">
+      <c r="A10" s="38"/>
+      <c r="B10" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="24">
         <v>7</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="26">
         <v>5</v>
       </c>
-      <c r="F10" s="35">
-        <v>0</v>
-      </c>
-      <c r="G10" s="38">
-        <v>0</v>
-      </c>
-      <c r="H10" s="35">
-        <v>0</v>
-      </c>
-      <c r="I10" s="35">
-        <v>11</v>
-      </c>
-      <c r="J10" s="35">
-        <v>0</v>
-      </c>
-      <c r="K10" s="35">
-        <v>0</v>
-      </c>
-      <c r="L10" s="35">
-        <v>0</v>
-      </c>
-      <c r="M10" s="40">
+      <c r="F10" s="26">
+        <v>0</v>
+      </c>
+      <c r="G10" s="29">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
+        <v>11</v>
+      </c>
+      <c r="J10" s="26">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26">
+        <v>0</v>
+      </c>
+      <c r="M10" s="30">
         <v>45799</v>
       </c>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="35"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="39"/>
-      <c r="B11" s="33" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="24">
         <v>1</v>
       </c>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="35">
-        <v>11</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="E11" s="26">
+        <v>11</v>
+      </c>
+      <c r="F11" s="26">
         <v>2</v>
       </c>
-      <c r="G11" s="35">
-        <v>0</v>
-      </c>
-      <c r="H11" s="35">
-        <v>0</v>
-      </c>
-      <c r="I11" s="35">
-        <v>11</v>
-      </c>
-      <c r="J11" s="35">
+      <c r="G11" s="26">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26">
+        <v>0</v>
+      </c>
+      <c r="I11" s="26">
+        <v>11</v>
+      </c>
+      <c r="J11" s="26">
         <v>1</v>
       </c>
-      <c r="K11" s="35">
-        <v>0</v>
-      </c>
-      <c r="L11" s="35">
-        <v>0</v>
-      </c>
-      <c r="M11" s="40">
+      <c r="K11" s="26">
+        <v>0</v>
+      </c>
+      <c r="L11" s="26">
+        <v>0</v>
+      </c>
+      <c r="M11" s="30">
         <v>45799</v>
       </c>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="44"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="34"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="39"/>
-      <c r="B12" s="33" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="24">
         <v>2</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="26">
         <v>2</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="26">
         <v>4</v>
       </c>
-      <c r="G12" s="35">
-        <v>0</v>
-      </c>
-      <c r="H12" s="35">
-        <v>0</v>
-      </c>
-      <c r="I12" s="35">
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26">
         <v>2</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="26">
         <v>4</v>
       </c>
-      <c r="K12" s="35">
-        <v>0</v>
-      </c>
-      <c r="L12" s="35">
-        <v>0</v>
-      </c>
-      <c r="M12" s="40">
+      <c r="K12" s="26">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26">
+        <v>0</v>
+      </c>
+      <c r="M12" s="30">
         <v>45798</v>
       </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="35"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="39"/>
-      <c r="B13" s="33" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="24">
         <v>3</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="26">
         <v>16</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="29">
         <v>14</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="26">
         <v>4</v>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="26">
         <v>24</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="26">
         <v>16</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="26">
         <v>14</v>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="26">
         <v>4</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="26">
         <v>20</v>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="30">
         <v>45798</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="35"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="39"/>
-      <c r="B14" s="33" t="s">
+      <c r="A14" s="38"/>
+      <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="24">
         <v>4</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="26">
         <v>2</v>
       </c>
-      <c r="F14" s="35">
-        <v>0</v>
-      </c>
-      <c r="G14" s="35">
-        <v>0</v>
-      </c>
-      <c r="H14" s="35">
-        <v>0</v>
-      </c>
-      <c r="I14" s="35">
+      <c r="F14" s="26">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26">
         <v>2</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="26">
         <v>4</v>
       </c>
-      <c r="K14" s="35">
-        <v>0</v>
-      </c>
-      <c r="L14" s="35">
-        <v>0</v>
-      </c>
-      <c r="M14" s="40">
+      <c r="K14" s="26">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30">
         <v>45798</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="35"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="26"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="39"/>
-      <c r="B15" s="33" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="24">
         <v>5</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="26">
         <v>5</v>
       </c>
-      <c r="F15" s="35">
-        <v>0</v>
-      </c>
-      <c r="G15" s="35">
-        <v>0</v>
-      </c>
-      <c r="H15" s="35">
-        <v>0</v>
-      </c>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="35"/>
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="39"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="24">
         <v>6</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="26">
         <v>4</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="26">
         <v>4</v>
       </c>
-      <c r="G16" s="35">
-        <v>0</v>
-      </c>
-      <c r="H16" s="35">
-        <v>0</v>
-      </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="35"/>
+      <c r="G16" s="26">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="39"/>
-      <c r="B17" s="33" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="24">
         <v>7</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="26">
         <v>10</v>
       </c>
-      <c r="F17" s="35">
-        <v>8</v>
-      </c>
-      <c r="G17" s="35">
-        <v>8</v>
-      </c>
-      <c r="H17" s="35">
+      <c r="F17" s="26">
+        <v>8</v>
+      </c>
+      <c r="G17" s="26">
+        <v>8</v>
+      </c>
+      <c r="H17" s="26">
         <v>20</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="26">
         <v>10</v>
       </c>
-      <c r="J17" s="35">
-        <v>8</v>
-      </c>
-      <c r="K17" s="35">
+      <c r="J17" s="26">
+        <v>8</v>
+      </c>
+      <c r="K17" s="26">
         <v>10</v>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="26">
         <v>13</v>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="30">
         <v>45798</v>
       </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="35"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16" ht="28.5">
-      <c r="A18" s="39"/>
-      <c r="B18" s="33" t="s">
+      <c r="A18" s="38"/>
+      <c r="B18" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="33">
-        <v>8</v>
-      </c>
-      <c r="D18" s="34" t="s">
+      <c r="C18" s="24">
+        <v>8</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="26">
         <v>9</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="26">
         <v>2</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="26">
         <v>2</v>
       </c>
-      <c r="H18" s="35">
+      <c r="H18" s="26">
         <v>2</v>
       </c>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="35"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="35"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="39"/>
-      <c r="B19" s="33" t="s">
+      <c r="A19" s="38"/>
+      <c r="B19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="24">
         <v>9</v>
       </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="35">
+      <c r="D19" s="27"/>
+      <c r="E19" s="26">
         <v>6</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="26">
         <v>6</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="26">
         <v>2</v>
       </c>
-      <c r="H19" s="35">
-        <v>0</v>
-      </c>
-      <c r="I19" s="35"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="35"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="35"/>
+      <c r="H19" s="26">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1718,7 +1718,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="28.5">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="39" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1727,7 +1727,7 @@
       <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="35" t="s">
         <v>40</v>
       </c>
       <c r="E2" s="5">
@@ -1762,14 +1762,14 @@
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" ht="28.5">
-      <c r="A3" s="25"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="35" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="5">
@@ -1804,14 +1804,14 @@
       <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="25"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="35" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="5">
@@ -1846,14 +1846,14 @@
       <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="25"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="36" t="s">
         <v>42</v>
       </c>
       <c r="E5" s="7">
@@ -1888,14 +1888,14 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="28.5">
-      <c r="A6" s="25"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="35" t="s">
         <v>43</v>
       </c>
       <c r="E6" s="5">
@@ -1930,14 +1930,14 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="25"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="37" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="5">
@@ -1972,14 +1972,14 @@
       <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="25"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="36" t="s">
         <v>44</v>
       </c>
       <c r="E8" s="5">
@@ -2014,14 +2014,14 @@
       <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="25"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="36" t="s">
         <v>44</v>
       </c>
       <c r="E9" s="5">
@@ -2056,14 +2056,14 @@
       <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="25"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="35" t="s">
         <v>44</v>
       </c>
       <c r="E10" s="5">
@@ -2098,14 +2098,14 @@
       <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="25"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="35" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="5">
@@ -2140,14 +2140,14 @@
       <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="25"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="36" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="5">
@@ -2182,14 +2182,14 @@
       <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="25"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="36" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="5">
@@ -2224,14 +2224,14 @@
       <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16" ht="28.5">
-      <c r="A14" s="25"/>
+      <c r="A14" s="40"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="35" t="s">
         <v>45</v>
       </c>
       <c r="E14" s="5">
@@ -2256,14 +2256,14 @@
       <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="25"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3">
         <v>5</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="35" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="5">
@@ -2288,14 +2288,14 @@
       <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="25"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="35" t="s">
         <v>46</v>
       </c>
       <c r="E16" s="5">
@@ -2320,14 +2320,14 @@
       <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="25"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="3">
         <v>7</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="35" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="5">
@@ -2362,14 +2362,14 @@
       <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="25"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="3">
         <v>8</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="35" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="5">
@@ -2404,14 +2404,14 @@
       <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="25"/>
+      <c r="A19" s="40"/>
       <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D19" s="45"/>
+      <c r="D19" s="35"/>
       <c r="E19" s="5">
         <v>6</v>
       </c>
@@ -2434,14 +2434,14 @@
       <c r="P19" s="5"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="25"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="21">
         <v>10</v>
       </c>
-      <c r="D20" s="46"/>
+      <c r="D20" s="36"/>
       <c r="E20" s="5">
         <v>6</v>
       </c>
@@ -2464,14 +2464,14 @@
       <c r="P20" s="5"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="26"/>
+      <c r="A21" s="41"/>
       <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="21">
         <v>11</v>
       </c>
-      <c r="D21" s="46"/>
+      <c r="D21" s="36"/>
       <c r="E21" s="5">
         <v>1</v>
       </c>
@@ -2572,7 +2572,7 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="42" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="11" t="s">
@@ -2604,7 +2604,7 @@
       <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="28"/>
+      <c r="A3" s="43"/>
       <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
@@ -2647,7 +2647,7 @@
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="28"/>
+      <c r="A4" s="43"/>
       <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
@@ -2690,12 +2690,12 @@
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="28"/>
+      <c r="A5" s="43"/>
       <c r="B5" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13">
@@ -2720,12 +2720,12 @@
       <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="29"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13">
@@ -2828,7 +2828,7 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="45" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="16" t="s">
@@ -2860,7 +2860,7 @@
       <c r="P2" s="17"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="31"/>
+      <c r="A3" s="46"/>
       <c r="B3" s="16" t="s">
         <v>11</v>
       </c>
@@ -2900,7 +2900,7 @@
       <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="31"/>
+      <c r="A4" s="46"/>
       <c r="B4" s="16" t="s">
         <v>11</v>
       </c>
@@ -2940,12 +2940,12 @@
       <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="31"/>
+      <c r="A5" s="46"/>
       <c r="B5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="18">
@@ -2970,12 +2970,12 @@
       <c r="P5" s="18"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="32"/>
+      <c r="A6" s="47"/>
       <c r="B6" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="18">
@@ -3013,6 +3013,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010074A154D0DC1E2447ADD5D8CA556ECA80" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a1fb4aabcd5adab87d9e1296b6f2d38">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22554d0a-1932-447e-b007-a2186b2152bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00325a2f7f39d3ee3bb3596f142ab400" ns2:_="">
     <xsd:import namespace="22554d0a-1932-447e-b007-a2186b2152bd"/>
@@ -3196,39 +3215,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3250,9 +3240,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BBB7B5-6822-4C1F-9098-2794F6D020F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A053C079-923F-47FD-A060-8E04017B095B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -947,13 +947,13 @@
         <v>0</v>
       </c>
       <c r="I2" s="26">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J2" s="26">
         <v>2</v>
       </c>
       <c r="K2" s="26">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L2" s="26">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="26">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J9" s="26">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="26">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J10" s="26">
         <v>0</v>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A20CD7-940C-4B9D-96BC-D80893742B93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364C7E60-C68E-4959-8E4C-2A1A03AA42C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" activeTab="3" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>MOD.</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>DAMAZ</t>
+  </si>
+  <si>
+    <t>Comparar colunas E com I, F com J, G com k, H com L. caso não tenham sido preenchidas as colunas I,J,K,L ainda é para desconsiderar. Caso a quantidade aumente ou diminua é para colocar. Quero um texo começando com um paragrafo fazendo a solicitação e abaixo separado por grupo (epf, dpf, ppf, pcf) as aulas M1.1, M1.2.... informando somente a solicitação de ajuste para mais ou para menos, caso não tenha ajuste não presida relacionar.</t>
   </si>
 </sst>
 </file>
@@ -252,18 +255,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -286,6 +283,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -414,15 +423,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -438,40 +438,67 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,15 +517,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -836,768 +854,788 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
-      <c r="A1" s="5"/>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:16" ht="30">
+      <c r="A1" s="26"/>
+      <c r="B1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="28">
-      <c r="A2" s="35" t="s">
+      <c r="P1" s="24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="28.5">
+      <c r="A2" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="26">
         <v>9</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="26">
         <v>9</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="5"/>
+      <c r="G2" s="26">
+        <v>0</v>
+      </c>
+      <c r="H2" s="26">
+        <v>0</v>
+      </c>
+      <c r="I2" s="26">
+        <v>16</v>
+      </c>
+      <c r="J2" s="26">
+        <v>2</v>
+      </c>
+      <c r="K2" s="26">
+        <v>8</v>
+      </c>
+      <c r="L2" s="26">
+        <v>0</v>
+      </c>
+      <c r="M2" s="30">
+        <v>46170</v>
+      </c>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="35"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="26">
         <v>9</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="26">
         <v>9</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="26">
+        <v>0</v>
+      </c>
+      <c r="H3" s="26">
         <v>4</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="4"/>
-    </row>
-    <row r="4" spans="1:16" ht="28">
-      <c r="A4" s="35"/>
-      <c r="B4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="I3" s="26">
+        <v>10</v>
+      </c>
+      <c r="J3" s="26">
+        <v>13</v>
+      </c>
+      <c r="K3" s="26">
+        <v>0</v>
+      </c>
+      <c r="L3" s="26">
+        <v>5</v>
+      </c>
+      <c r="M3" s="30">
+        <v>46169</v>
+      </c>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="31"/>
+    </row>
+    <row r="4" spans="1:16" ht="28.5">
+      <c r="A4" s="38"/>
+      <c r="B4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="24">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="26">
         <v>13</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="26">
+        <v>0</v>
+      </c>
+      <c r="G4" s="26">
         <v>15</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="26">
         <v>15</v>
       </c>
-      <c r="I4" s="31">
-        <v>8</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="I4" s="26">
+        <v>8</v>
+      </c>
+      <c r="J4" s="26">
         <v>5</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="26">
         <v>15</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="26">
         <v>10</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="30">
         <v>45798</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="35"/>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3">
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="26"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="38"/>
+      <c r="B5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="24">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="28">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="26">
         <v>2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="26">
         <v>17</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="26">
         <v>20</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="26">
         <v>12</v>
       </c>
-      <c r="J5" s="31">
+      <c r="J5" s="26">
         <v>1</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="26">
         <v>17</v>
       </c>
-      <c r="L5" s="31">
+      <c r="L5" s="26">
         <v>15</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="30">
         <v>45798</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="5"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="26"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="35"/>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="A6" s="38"/>
+      <c r="B6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="26">
         <v>10</v>
       </c>
-      <c r="F6" s="5">
-        <v>8</v>
-      </c>
-      <c r="G6" s="5">
-        <v>8</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="F6" s="26">
+        <v>8</v>
+      </c>
+      <c r="G6" s="26">
+        <v>8</v>
+      </c>
+      <c r="H6" s="26">
         <v>15</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="26">
         <v>10</v>
       </c>
-      <c r="J6" s="5">
-        <v>8</v>
-      </c>
-      <c r="K6" s="31">
+      <c r="J6" s="26">
+        <v>8</v>
+      </c>
+      <c r="K6" s="26">
         <v>16</v>
       </c>
-      <c r="L6" s="31">
-        <v>8</v>
-      </c>
-      <c r="M6" s="6">
+      <c r="L6" s="26">
+        <v>8</v>
+      </c>
+      <c r="M6" s="30">
         <v>45798</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="8"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="32"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="35"/>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="A7" s="38"/>
+      <c r="B7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="24">
         <v>4</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="26">
         <v>13</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="26">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26">
         <v>10</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="26">
         <v>18</v>
       </c>
-      <c r="I7" s="31">
-        <v>8</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="I7" s="26">
+        <v>8</v>
+      </c>
+      <c r="J7" s="26">
         <v>10</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="26">
         <v>10</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="26">
         <v>16</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="30">
         <v>45798</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="9"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="33"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="35"/>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="A8" s="38"/>
+      <c r="B8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="24">
         <v>5</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="5">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5">
-        <v>8</v>
-      </c>
-      <c r="G8" s="5">
+      <c r="E8" s="26">
+        <v>11</v>
+      </c>
+      <c r="F8" s="26">
+        <v>8</v>
+      </c>
+      <c r="G8" s="26">
         <v>24</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="26">
         <v>23</v>
       </c>
-      <c r="I8" s="5">
-        <v>11</v>
-      </c>
-      <c r="J8" s="5">
-        <v>8</v>
-      </c>
-      <c r="K8" s="5">
+      <c r="I8" s="26">
+        <v>11</v>
+      </c>
+      <c r="J8" s="26">
+        <v>8</v>
+      </c>
+      <c r="K8" s="26">
         <v>24</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="26">
         <v>21</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="30">
         <v>45799</v>
       </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="5"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="26"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="35"/>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="A9" s="38"/>
+      <c r="B9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="24">
         <v>6</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="26">
         <v>10</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="26">
         <v>0</v>
       </c>
       <c r="G9" s="29">
         <v>8</v>
       </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="H9" s="26">
+        <v>0</v>
+      </c>
+      <c r="I9" s="26">
         <v>10</v>
       </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>8</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="J9" s="26">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26">
+        <v>8</v>
+      </c>
+      <c r="L9" s="26">
+        <v>0</v>
+      </c>
+      <c r="M9" s="30">
         <v>45799</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="5"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="35"/>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="A10" s="38"/>
+      <c r="B10" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="24">
         <v>7</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="26">
         <v>5</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="26">
         <v>0</v>
       </c>
       <c r="G10" s="29">
         <v>0</v>
       </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="26">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26">
         <v>5</v>
       </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="J10" s="26">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26">
+        <v>0</v>
+      </c>
+      <c r="M10" s="30">
         <v>45799</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="5"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="35"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="24">
         <v>1</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="5">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="E11" s="26">
+        <v>11</v>
+      </c>
+      <c r="F11" s="26">
         <v>2</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>11</v>
-      </c>
-      <c r="J11" s="5">
+      <c r="G11" s="26">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26">
+        <v>0</v>
+      </c>
+      <c r="I11" s="26">
+        <v>11</v>
+      </c>
+      <c r="J11" s="26">
         <v>1</v>
       </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="K11" s="26">
+        <v>0</v>
+      </c>
+      <c r="L11" s="26">
+        <v>0</v>
+      </c>
+      <c r="M11" s="30">
         <v>45799</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="10"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="34"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="35"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="38"/>
+      <c r="B12" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="24">
         <v>2</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="26">
         <v>2</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="26">
         <v>4</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
+        <v>0</v>
+      </c>
+      <c r="I12" s="26">
         <v>2</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="26">
         <v>4</v>
       </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
+      <c r="K12" s="26">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26">
+        <v>0</v>
+      </c>
+      <c r="M12" s="30">
         <v>45798</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="5"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="35"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="24">
         <v>3</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="26">
         <v>16</v>
       </c>
       <c r="F13" s="29">
         <v>14</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="26">
         <v>4</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="26">
         <v>24</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="26">
         <v>16</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="26">
         <v>14</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="26">
         <v>4</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="26">
         <v>20</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="30">
         <v>45798</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="5"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="35"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="38"/>
+      <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="24">
         <v>4</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="26">
         <v>2</v>
       </c>
-      <c r="F14" s="5">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="F14" s="26">
+        <v>0</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26">
         <v>2</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="26">
         <v>4</v>
       </c>
-      <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" s="5">
-        <v>0</v>
-      </c>
-      <c r="M14" s="6">
+      <c r="K14" s="26">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30">
         <v>45798</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="5"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="26"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="35"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="24">
         <v>5</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="26">
         <v>5</v>
       </c>
-      <c r="F15" s="5">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="5"/>
+      <c r="F15" s="26">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0</v>
+      </c>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30"/>
+      <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="35"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="38"/>
+      <c r="B16" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="24">
         <v>6</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="26">
         <v>4</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="26">
         <v>4</v>
       </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="5"/>
+      <c r="G16" s="26">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26">
+        <v>0</v>
+      </c>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="35"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="38"/>
+      <c r="B17" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="24">
         <v>7</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="26">
         <v>10</v>
       </c>
-      <c r="F17" s="5">
-        <v>8</v>
-      </c>
-      <c r="G17" s="5">
-        <v>8</v>
-      </c>
-      <c r="H17" s="5">
+      <c r="F17" s="26">
+        <v>8</v>
+      </c>
+      <c r="G17" s="26">
+        <v>8</v>
+      </c>
+      <c r="H17" s="26">
         <v>20</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="26">
         <v>10</v>
       </c>
-      <c r="J17" s="5">
-        <v>8</v>
-      </c>
-      <c r="K17" s="31">
+      <c r="J17" s="26">
+        <v>8</v>
+      </c>
+      <c r="K17" s="26">
         <v>10</v>
       </c>
-      <c r="L17" s="31">
+      <c r="L17" s="26">
         <v>13</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="30">
         <v>45798</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="5"/>
-    </row>
-    <row r="18" spans="1:16" ht="28">
-      <c r="A18" s="35"/>
-      <c r="B18" s="3" t="s">
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="26"/>
+    </row>
+    <row r="18" spans="1:16" ht="28.5">
+      <c r="A18" s="38"/>
+      <c r="B18" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="3">
-        <v>8</v>
-      </c>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="24">
+        <v>8</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="26">
         <v>9</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="26">
         <v>2</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="26">
         <v>2</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="26">
         <v>2</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="5"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="35"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="38"/>
+      <c r="B19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="24">
         <v>9</v>
       </c>
-      <c r="D19" s="33"/>
-      <c r="E19" s="5">
+      <c r="D19" s="27"/>
+      <c r="E19" s="26">
         <v>6</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="26">
         <v>6</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="26">
         <v>2</v>
       </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="5"/>
+      <c r="H19" s="26">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1612,828 +1650,848 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
-      <c r="A1" s="13"/>
-      <c r="B1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
+    <row r="1" spans="1:16" ht="30">
+      <c r="A1" s="5"/>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="28">
-      <c r="A2" s="36" t="s">
+      <c r="P1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="28.5">
+      <c r="A2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="5">
         <v>9</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="5">
         <v>9</v>
       </c>
-      <c r="G2" s="13">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="13"/>
-    </row>
-    <row r="3" spans="1:16" ht="28">
-      <c r="A3" s="37"/>
-      <c r="B3" s="11" t="s">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>16</v>
+      </c>
+      <c r="J2" s="5">
+        <v>6</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <v>46170</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" ht="28.5">
+      <c r="A3" s="40"/>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="5">
         <v>15</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="5">
         <v>5</v>
       </c>
-      <c r="G3" s="13">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
         <v>4</v>
       </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="12"/>
+      <c r="I3" s="5">
+        <v>25</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="6">
+        <v>46170</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="4"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="37"/>
-      <c r="B4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="11">
+      <c r="A4" s="40"/>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="5">
         <v>12</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="5">
         <v>17</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="5">
         <v>20</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="5">
         <v>12</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="5">
         <v>17</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="5">
         <v>15</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="6">
         <v>45798</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" ht="14.5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="11">
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="40"/>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="7">
         <v>6</v>
       </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0</v>
-      </c>
-      <c r="I5" s="13">
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
         <v>6</v>
       </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="13">
-        <v>0</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0</v>
-      </c>
-      <c r="M5" s="14">
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6">
         <v>45798</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" ht="28">
-      <c r="A6" s="37"/>
-      <c r="B6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="11">
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" ht="28.5">
+      <c r="A6" s="40"/>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="5">
         <v>10</v>
       </c>
-      <c r="F6" s="13">
-        <v>8</v>
-      </c>
-      <c r="G6" s="13">
-        <v>8</v>
-      </c>
-      <c r="H6" s="13">
+      <c r="F6" s="5">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5">
         <v>15</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="5">
         <v>10</v>
       </c>
-      <c r="J6" s="13">
-        <v>8</v>
-      </c>
-      <c r="K6" s="31">
+      <c r="J6" s="5">
+        <v>8</v>
+      </c>
+      <c r="K6" s="5">
         <v>16</v>
       </c>
-      <c r="L6" s="31">
+      <c r="L6" s="5">
         <v>18</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="6">
         <v>45798</v>
       </c>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="16"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="37"/>
-      <c r="B7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="11">
+      <c r="A7" s="40"/>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3">
         <v>4</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="5">
         <v>13</v>
       </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
         <v>10</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="5">
         <v>18</v>
       </c>
-      <c r="I7" s="31">
-        <v>8</v>
-      </c>
-      <c r="J7" s="31">
+      <c r="I7" s="5">
+        <v>8</v>
+      </c>
+      <c r="J7" s="5">
         <v>10</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="5">
         <v>10</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="5">
         <v>16</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="6">
         <v>45798</v>
       </c>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="17"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="9"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="37"/>
-      <c r="B8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="A8" s="40"/>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
         <v>5</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="5">
         <v>6</v>
       </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="31">
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
         <v>5</v>
       </c>
-      <c r="J8" s="13">
-        <v>0</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>0</v>
-      </c>
-      <c r="M8" s="14">
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
         <v>45798</v>
       </c>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="13"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="37"/>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="11">
+      <c r="A9" s="40"/>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="13">
-        <v>11</v>
-      </c>
-      <c r="F9" s="13">
-        <v>8</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="E9" s="5">
+        <v>11</v>
+      </c>
+      <c r="F9" s="5">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
         <v>24</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="5">
         <v>23</v>
       </c>
-      <c r="I9" s="13">
-        <v>11</v>
-      </c>
-      <c r="J9" s="13">
-        <v>8</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="I9" s="5">
+        <v>11</v>
+      </c>
+      <c r="J9" s="5">
+        <v>8</v>
+      </c>
+      <c r="K9" s="5">
         <v>24</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="5">
         <v>21</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="6">
         <v>45798</v>
       </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="13"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="37"/>
-      <c r="B10" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11">
+      <c r="A10" s="40"/>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
         <v>7</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="5">
         <v>10</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="31">
-        <v>11</v>
-      </c>
-      <c r="J10" s="31">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>11</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
         <v>45798</v>
       </c>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="13"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="37"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="40"/>
+      <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="3">
         <v>1</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="13">
-        <v>11</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="5">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5">
         <v>2</v>
       </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
-        <v>11</v>
-      </c>
-      <c r="J11" s="13">
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>11</v>
+      </c>
+      <c r="J11" s="5">
         <v>1</v>
       </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14">
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6">
         <v>45799</v>
       </c>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="18"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="37"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="40"/>
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="5">
         <v>2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="5">
         <v>4</v>
       </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
         <v>2</v>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="5">
         <v>4</v>
       </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="14">
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
         <v>45798</v>
       </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="13"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="37"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="40"/>
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="5">
         <v>16</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="5">
         <v>14</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="5">
         <v>4</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="5">
         <v>24</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="5">
         <v>16</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="5">
         <v>14</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="5">
         <v>4</v>
       </c>
-      <c r="L13" s="31">
+      <c r="L13" s="5">
         <v>20</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="6">
         <v>45798</v>
       </c>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" ht="28">
-      <c r="A14" s="37"/>
-      <c r="B14" s="11" t="s">
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" spans="1:16" ht="28.5">
+      <c r="A14" s="40"/>
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="3">
         <v>4</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="5">
         <v>6</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="5">
         <v>2</v>
       </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="13"/>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="37"/>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="40"/>
+      <c r="B15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="3">
         <v>5</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="13">
-        <v>8</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="13"/>
+      <c r="E15" s="5">
+        <v>8</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="37"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="40"/>
+      <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="3">
         <v>6</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="13">
-        <v>8</v>
-      </c>
-      <c r="F16" s="13">
+      <c r="E16" s="5">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5">
         <v>2</v>
       </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="13"/>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="5"/>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="37"/>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="40"/>
+      <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="3">
         <v>7</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="5">
         <v>2</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="5">
         <v>2</v>
       </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-      <c r="I17" s="31">
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
         <v>5</v>
       </c>
-      <c r="J17" s="13">
-        <v>0</v>
-      </c>
-      <c r="K17" s="13">
-        <v>0</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0</v>
-      </c>
-      <c r="M17" s="14">
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="6">
         <v>45798</v>
       </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="13"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="5"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="37"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="40"/>
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="11">
-        <v>8</v>
-      </c>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="3">
+        <v>8</v>
+      </c>
+      <c r="D18" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="5">
         <v>10</v>
       </c>
-      <c r="F18" s="13">
-        <v>8</v>
-      </c>
-      <c r="G18" s="13">
-        <v>8</v>
-      </c>
-      <c r="H18" s="13">
+      <c r="F18" s="5">
+        <v>8</v>
+      </c>
+      <c r="G18" s="5">
+        <v>8</v>
+      </c>
+      <c r="H18" s="5">
         <v>20</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="5">
         <v>10</v>
       </c>
-      <c r="J18" s="13">
-        <v>8</v>
-      </c>
-      <c r="K18" s="31">
+      <c r="J18" s="5">
+        <v>8</v>
+      </c>
+      <c r="K18" s="5">
         <v>10</v>
       </c>
-      <c r="L18" s="31">
+      <c r="L18" s="5">
         <v>13</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="6">
         <v>45798</v>
       </c>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="13"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="5"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="37"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="40"/>
+      <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="3">
         <v>9</v>
       </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="13">
+      <c r="D19" s="35"/>
+      <c r="E19" s="5">
         <v>6</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="5">
         <v>2</v>
       </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="13"/>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="5"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="37"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="40"/>
+      <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="21">
         <v>10</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="13">
+      <c r="D20" s="36"/>
+      <c r="E20" s="5">
         <v>6</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="5">
         <v>6</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="5">
         <v>2</v>
       </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="38"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="41"/>
+      <c r="B21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="30">
-        <v>11</v>
-      </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="13">
+      <c r="C21" s="21">
+        <v>11</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="5">
         <v>1</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="5">
         <v>4</v>
       </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2446,250 +2504,250 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="28">
-      <c r="A1" s="21"/>
-      <c r="B1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="19" t="s">
+    <row r="1" spans="1:19" ht="30">
+      <c r="A1" s="13"/>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21">
+      <c r="D2" s="12"/>
+      <c r="E2" s="13">
         <v>14</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="13">
         <v>6</v>
       </c>
-      <c r="G2" s="21">
-        <v>0</v>
-      </c>
-      <c r="H2" s="21">
+      <c r="G2" s="13">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13">
         <v>15</v>
       </c>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="21"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="13"/>
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1">
-      <c r="A3" s="40"/>
-      <c r="B3" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="19">
+      <c r="A3" s="43"/>
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="11">
         <v>1</v>
       </c>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21">
+      <c r="D3" s="12"/>
+      <c r="E3" s="13">
         <v>10</v>
       </c>
-      <c r="F3" s="21">
-        <v>8</v>
-      </c>
-      <c r="G3" s="21">
-        <v>8</v>
-      </c>
-      <c r="H3" s="21">
+      <c r="F3" s="13">
+        <v>8</v>
+      </c>
+      <c r="G3" s="13">
+        <v>8</v>
+      </c>
+      <c r="H3" s="13">
         <v>15</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="23">
         <v>7</v>
       </c>
-      <c r="J3" s="31">
+      <c r="J3" s="23">
         <v>5</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="23">
         <v>10</v>
       </c>
-      <c r="L3" s="31">
-        <v>11</v>
-      </c>
-      <c r="M3" s="22">
+      <c r="L3" s="23">
+        <v>11</v>
+      </c>
+      <c r="M3" s="14">
         <v>45798</v>
       </c>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="21"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="13"/>
       <c r="R3" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" customHeight="1">
-      <c r="A4" s="40"/>
-      <c r="B4" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="A4" s="43"/>
+      <c r="B4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="11">
         <v>2</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="23">
+      <c r="D4" s="12"/>
+      <c r="E4" s="15">
         <v>13</v>
       </c>
-      <c r="F4" s="21">
-        <v>0</v>
-      </c>
-      <c r="G4" s="21">
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13">
         <v>10</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="13">
         <v>18</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="23">
         <v>6</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="23">
         <v>6</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="23">
         <v>6</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="23">
         <v>10</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="14">
         <v>45798</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="21"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="13"/>
       <c r="S4" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1">
-      <c r="A5" s="40"/>
-      <c r="B5" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="19">
-        <v>5</v>
-      </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21">
-        <v>11</v>
-      </c>
-      <c r="F5" s="21">
-        <v>8</v>
-      </c>
-      <c r="G5" s="21">
+      <c r="A5" s="43"/>
+      <c r="B5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="11">
+        <v>3</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13">
+        <v>11</v>
+      </c>
+      <c r="F5" s="13">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13">
         <v>24</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="13">
         <v>23</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="21"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="13"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="19">
-        <v>6</v>
-      </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="21">
+      <c r="A6" s="44"/>
+      <c r="B6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13">
         <v>2</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="13">
         <v>4</v>
       </c>
-      <c r="G6" s="21">
-        <v>0</v>
-      </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="G6" s="13">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2701,245 +2759,250 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
-    <col min="2" max="2" width="8.83203125" style="2"/>
-    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.875" style="1"/>
+    <col min="2" max="2" width="8.875" style="2"/>
+    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="17" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28">
-      <c r="A1" s="26"/>
-      <c r="B1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="24" t="s">
+    <row r="1" spans="1:16" ht="30">
+      <c r="A1" s="18"/>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="24" t="s">
+      <c r="K1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="26">
+      <c r="D2" s="17"/>
+      <c r="E2" s="18">
         <v>14</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="18">
         <v>6</v>
       </c>
-      <c r="G2" s="26">
-        <v>0</v>
-      </c>
-      <c r="H2" s="26">
+      <c r="G2" s="18">
+        <v>0</v>
+      </c>
+      <c r="H2" s="18">
         <v>15</v>
       </c>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="25"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="17"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="A3" s="43"/>
-      <c r="B3" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="24">
+      <c r="A3" s="46"/>
+      <c r="B3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="16">
         <v>1</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="26">
+      <c r="D3" s="17"/>
+      <c r="E3" s="18">
         <v>10</v>
       </c>
-      <c r="F3" s="26">
-        <v>8</v>
-      </c>
-      <c r="G3" s="26">
-        <v>8</v>
-      </c>
-      <c r="H3" s="26">
+      <c r="F3" s="18">
+        <v>8</v>
+      </c>
+      <c r="G3" s="18">
+        <v>8</v>
+      </c>
+      <c r="H3" s="18">
         <v>15</v>
       </c>
-      <c r="I3" s="31">
+      <c r="I3" s="22">
         <v>10</v>
       </c>
-      <c r="J3" s="31">
-        <v>8</v>
-      </c>
-      <c r="K3" s="31">
+      <c r="J3" s="22">
+        <v>8</v>
+      </c>
+      <c r="K3" s="22">
         <v>16</v>
       </c>
-      <c r="L3" s="31">
+      <c r="L3" s="22">
         <v>18</v>
       </c>
-      <c r="M3" s="27">
+      <c r="M3" s="19">
         <v>45798</v>
       </c>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="26"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:16" ht="15" customHeight="1">
-      <c r="A4" s="43"/>
-      <c r="B4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="A4" s="46"/>
+      <c r="B4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="16">
         <v>2</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="28">
+      <c r="D4" s="17"/>
+      <c r="E4" s="20">
         <v>13</v>
       </c>
-      <c r="F4" s="26">
-        <v>0</v>
-      </c>
-      <c r="G4" s="26">
+      <c r="F4" s="18">
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
         <v>10</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="18">
         <v>18</v>
       </c>
-      <c r="I4" s="31">
-        <v>8</v>
-      </c>
-      <c r="J4" s="31">
+      <c r="I4" s="22">
+        <v>8</v>
+      </c>
+      <c r="J4" s="22">
         <v>10</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="22">
         <v>10</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="22">
         <v>16</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="19">
         <v>45798</v>
       </c>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="26"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="43"/>
-      <c r="B5" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="24">
-        <v>5</v>
-      </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="26">
-        <v>11</v>
-      </c>
-      <c r="F5" s="26">
-        <v>8</v>
-      </c>
-      <c r="G5" s="26">
+      <c r="A5" s="46"/>
+      <c r="B5" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16">
+        <v>3</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="18">
+        <v>11</v>
+      </c>
+      <c r="F5" s="18">
+        <v>8</v>
+      </c>
+      <c r="G5" s="18">
         <v>24</v>
       </c>
-      <c r="H5" s="26">
+      <c r="H5" s="18">
         <v>23</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="26"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="18"/>
     </row>
     <row r="6" spans="1:16" ht="15" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="24">
-        <v>6</v>
-      </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="26">
+      <c r="A6" s="47"/>
+      <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="16">
+        <v>4</v>
+      </c>
+      <c r="D6" s="17"/>
+      <c r="E6" s="18">
         <v>2</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="18">
         <v>4</v>
       </c>
-      <c r="G6" s="26">
-        <v>0</v>
-      </c>
-      <c r="H6" s="26">
-        <v>0</v>
-      </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="26"/>
+      <c r="G6" s="18">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="18"/>
+    </row>
+    <row r="12" spans="1:16" ht="409.5">
+      <c r="F12" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2960,6 +3023,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010074A154D0DC1E2447ADD5D8CA556ECA80" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a1fb4aabcd5adab87d9e1296b6f2d38">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22554d0a-1932-447e-b007-a2186b2152bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00325a2f7f39d3ee3bb3596f142ab400" ns2:_="">
     <xsd:import namespace="22554d0a-1932-447e-b007-a2186b2152bd"/>
@@ -3143,15 +3215,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
   <ds:schemaRefs>
@@ -3169,6 +3232,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3186,14 +3257,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" enabled="0" method="" siteId="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" removed="1"/>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcel.mfpm\Downloads\REFORMULAÇÃO - LARISSA\PROJETO PA E PD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364C7E60-C68E-4959-8E4C-2A1A03AA42C8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765FA486-D360-401B-AD1D-85502E617BF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14385" windowHeight="4065" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14390" windowHeight="4070" activeTab="2" xr2:uid="{A872491A-373F-4F8D-9252-91ADE5CA8578}"/>
   </bookViews>
   <sheets>
     <sheet name="EPF" sheetId="1" r:id="rId1"/>
@@ -854,26 +854,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DF0423F-3F79-4C1A-8E98-72864AA85B9D}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="26"/>
       <c r="B1" s="24" t="s">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.5">
+    <row r="2" spans="1:16" ht="28">
       <c r="A2" s="38" t="s">
         <v>14</v>
       </c>
@@ -1007,7 +1007,7 @@
       <c r="O3" s="30"/>
       <c r="P3" s="31"/>
     </row>
-    <row r="4" spans="1:16" ht="28.5">
+    <row r="4" spans="1:16" ht="28">
       <c r="A4" s="38"/>
       <c r="B4" s="24" t="s">
         <v>11</v>
@@ -1043,13 +1043,13 @@
         <v>10</v>
       </c>
       <c r="M4" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N4" s="30"/>
       <c r="O4" s="30"/>
       <c r="P4" s="26"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="38"/>
       <c r="B5" s="24" t="s">
         <v>11</v>
@@ -1085,7 +1085,7 @@
         <v>15</v>
       </c>
       <c r="M5" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N5" s="30"/>
       <c r="O5" s="30"/>
@@ -1127,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="M6" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N6" s="30"/>
       <c r="O6" s="30"/>
@@ -1157,10 +1157,10 @@
         <v>18</v>
       </c>
       <c r="I7" s="26">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J7" s="26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K7" s="26">
         <v>10</v>
@@ -1169,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="M7" s="30">
-        <v>45798</v>
+        <v>46204</v>
       </c>
       <c r="N7" s="30"/>
       <c r="O7" s="30"/>
@@ -1211,7 +1211,7 @@
         <v>21</v>
       </c>
       <c r="M8" s="30">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="N8" s="30"/>
       <c r="O8" s="30"/>
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="30">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="N9" s="30"/>
       <c r="O9" s="30"/>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="30">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="N10" s="30"/>
       <c r="O10" s="30"/>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="30">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="N11" s="30"/>
       <c r="O11" s="30"/>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
@@ -1421,7 +1421,7 @@
         <v>20</v>
       </c>
       <c r="M13" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N13" s="30"/>
       <c r="O13" s="30"/>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="30">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N14" s="30"/>
       <c r="O14" s="30"/>
@@ -1575,7 +1575,7 @@
       <c r="O17" s="30"/>
       <c r="P17" s="26"/>
     </row>
-    <row r="18" spans="1:16" ht="28.5">
+    <row r="18" spans="1:16" ht="28">
       <c r="A18" s="38"/>
       <c r="B18" s="24" t="s">
         <v>12</v>
@@ -1650,26 +1650,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD951558-3DEF-4573-8D77-A22E116C5C48}">
   <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="5"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1717,7 +1717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="28.5">
+    <row r="2" spans="1:16" ht="28">
       <c r="A2" s="39" t="s">
         <v>15</v>
       </c>
@@ -1761,7 +1761,7 @@
       <c r="O2" s="6"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16" ht="28.5">
+    <row r="3" spans="1:16" ht="28">
       <c r="A3" s="40"/>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -1845,7 +1845,7 @@
       <c r="O4" s="6"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" ht="14.5">
       <c r="A5" s="40"/>
       <c r="B5" s="3" t="s">
         <v>11</v>
@@ -1887,7 +1887,7 @@
       <c r="O5" s="6"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" ht="28.5">
+    <row r="6" spans="1:16" ht="28">
       <c r="A6" s="40"/>
       <c r="B6" s="3" t="s">
         <v>11</v>
@@ -1953,10 +1953,10 @@
         <v>18</v>
       </c>
       <c r="I7" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J7" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K7" s="5">
         <v>10</v>
@@ -1965,7 +1965,7 @@
         <v>16</v>
       </c>
       <c r="M7" s="6">
-        <v>45798</v>
+        <v>46204</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
@@ -2007,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -2049,7 +2049,7 @@
         <v>21</v>
       </c>
       <c r="M9" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="6">
-        <v>45799</v>
+        <v>46164</v>
       </c>
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
@@ -2217,13 +2217,13 @@
         <v>20</v>
       </c>
       <c r="M13" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="5"/>
     </row>
-    <row r="14" spans="1:16" ht="28.5">
+    <row r="14" spans="1:16" ht="28">
       <c r="A14" s="40"/>
       <c r="B14" s="3" t="s">
         <v>12</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
@@ -2397,7 +2397,7 @@
         <v>13</v>
       </c>
       <c r="M18" s="6">
-        <v>45798</v>
+        <v>46163</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -2504,26 +2504,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65613A53-C102-4256-AEC9-305787A9B0EA}">
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="30">
+    <row r="1" spans="1:19" ht="28">
       <c r="A1" s="13"/>
       <c r="B1" s="11" t="s">
         <v>0</v>
@@ -2625,19 +2625,19 @@
         <v>15</v>
       </c>
       <c r="I3" s="23">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J3" s="23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K3" s="23">
         <v>10</v>
       </c>
       <c r="L3" s="23">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M3" s="14">
-        <v>45798</v>
+        <v>46204</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14"/>
@@ -2760,26 +2760,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF0F1BD-DA81-409F-B879-31CA2FD3E4BB}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="8.875" style="1"/>
-    <col min="2" max="2" width="8.875" style="2"/>
-    <col min="3" max="3" width="8.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="8.83203125" style="2"/>
+    <col min="3" max="3" width="8.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.58203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.58203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.08203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.58203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.08203125" style="1" customWidth="1"/>
     <col min="14" max="15" width="17" style="1" customWidth="1"/>
     <col min="16" max="16" width="38.5" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.875" style="1"/>
+    <col min="17" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30">
+    <row r="1" spans="1:16" ht="28">
       <c r="A1" s="18"/>
       <c r="B1" s="16" t="s">
         <v>0</v>
@@ -2881,19 +2881,19 @@
         <v>15</v>
       </c>
       <c r="I3" s="22">
+        <v>13</v>
+      </c>
+      <c r="J3" s="22">
+        <v>0</v>
+      </c>
+      <c r="K3" s="22">
         <v>10</v>
       </c>
-      <c r="J3" s="22">
-        <v>8</v>
-      </c>
-      <c r="K3" s="22">
+      <c r="L3" s="22">
         <v>16</v>
       </c>
-      <c r="L3" s="22">
-        <v>18</v>
-      </c>
       <c r="M3" s="19">
-        <v>45798</v>
+        <v>46204</v>
       </c>
       <c r="N3" s="19"/>
       <c r="O3" s="19"/>
@@ -3013,25 +3013,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010074A154D0DC1E2447ADD5D8CA556ECA80" ma:contentTypeVersion="11" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a1fb4aabcd5adab87d9e1296b6f2d38">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="22554d0a-1932-447e-b007-a2186b2152bd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="00325a2f7f39d3ee3bb3596f142ab400" ns2:_="">
     <xsd:import namespace="22554d0a-1932-447e-b007-a2186b2152bd"/>
@@ -3215,31 +3196,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="22554d0a-1932-447e-b007-a2186b2152bd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DEF66AC-E308-43BF-9F64-94748D5DACCB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3257,6 +3233,30 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D86BB587-35FF-4C72-A3B4-30D223CD8217}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D844D4EE-45BA-4D0C-B92D-0FE188981EFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="22554d0a-1932-447e-b007-a2186b2152bd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" enabled="0" method="" siteId="{56c1e2fb-87c1-4de0-a6ac-d0566c08ce66}" removed="1"/>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -2194,6 +2194,9 @@
       <c r="H6">
         <v>0</v>
       </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="F12" t="str">

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:Q19"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -448,6 +448,9 @@
       <c r="P1" t="str">
         <v>OBS. LUCIANA</v>
       </c>
+      <c r="Q1" t="str">
+        <v>ANDAMENTO</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -489,6 +492,9 @@
       <c r="M2" t="str">
         <v>05/28/2026</v>
       </c>
+      <c r="Q2" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="str">
@@ -527,6 +533,9 @@
       <c r="M3" t="str">
         <v>05/27/2026</v>
       </c>
+      <c r="Q3" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="str">
@@ -565,6 +574,9 @@
       <c r="M4" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="str">
@@ -603,6 +615,9 @@
       <c r="M5" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q5" t="str">
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
@@ -641,6 +656,9 @@
       <c r="M6" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q6" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="str">
@@ -679,6 +697,9 @@
       <c r="M7" t="str">
         <v>07/01/2026</v>
       </c>
+      <c r="Q7" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="str">
@@ -717,6 +738,9 @@
       <c r="M8" t="str">
         <v>05/22/2026</v>
       </c>
+      <c r="Q8" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="str">
@@ -755,6 +779,9 @@
       <c r="M9" t="str">
         <v>05/22/2026</v>
       </c>
+      <c r="Q9" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="str">
@@ -793,6 +820,9 @@
       <c r="M10" t="str">
         <v>05/22/2026</v>
       </c>
+      <c r="Q10" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="str">
@@ -831,6 +861,9 @@
       <c r="M11" t="str">
         <v>05/22/2026</v>
       </c>
+      <c r="Q11" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="str">
@@ -869,6 +902,9 @@
       <c r="M12" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q12" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="str">
@@ -907,6 +943,9 @@
       <c r="M13" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q13" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="str">
@@ -945,6 +984,9 @@
       <c r="M14" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q14" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="str">
@@ -968,6 +1010,9 @@
       <c r="H15">
         <v>0</v>
       </c>
+      <c r="Q15" t="str">
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="str">
@@ -991,6 +1036,21 @@
       <c r="H16">
         <v>0</v>
       </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="str">
@@ -1029,6 +1089,9 @@
       <c r="M17" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q17" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="str">
@@ -1052,6 +1115,21 @@
       <c r="H18">
         <v>2</v>
       </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="str">
@@ -1071,6 +1149,9 @@
       </c>
       <c r="H19">
         <v>0</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Pendente</v>
       </c>
     </row>
   </sheetData>
@@ -1079,14 +1160,14 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q19"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -1134,6 +1215,9 @@
       <c r="P1" t="str">
         <v>OBS. LUCIANA</v>
       </c>
+      <c r="Q1" t="str">
+        <v>ANDAMENTO</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1175,6 +1259,9 @@
       <c r="M2" t="str">
         <v>05/28/2026</v>
       </c>
+      <c r="Q2" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="str">
@@ -1213,6 +1300,9 @@
       <c r="M3" t="str">
         <v>05/28/2026</v>
       </c>
+      <c r="Q3" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="str">
@@ -1251,6 +1341,9 @@
       <c r="M4" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="str">
@@ -1289,6 +1382,9 @@
       <c r="M5" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q5" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
@@ -1327,6 +1423,9 @@
       <c r="M6" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q6" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="str">
@@ -1365,6 +1464,9 @@
       <c r="M7" t="str">
         <v>07/01/2026</v>
       </c>
+      <c r="Q7" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="str">
@@ -1403,6 +1505,9 @@
       <c r="M8" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q8" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="str">
@@ -1441,6 +1546,9 @@
       <c r="M9" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q9" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="str">
@@ -1479,6 +1587,9 @@
       <c r="M10" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q10" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="str">
@@ -1517,6 +1628,9 @@
       <c r="M11" t="str">
         <v>05/22/2026</v>
       </c>
+      <c r="Q11" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="str">
@@ -1555,6 +1669,9 @@
       <c r="M12" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q12" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="str">
@@ -1593,6 +1710,9 @@
       <c r="M13" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q13" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="str">
@@ -1616,6 +1736,9 @@
       <c r="H14">
         <v>0</v>
       </c>
+      <c r="Q14" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="str">
@@ -1639,6 +1762,9 @@
       <c r="H15">
         <v>0</v>
       </c>
+      <c r="Q15" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="str">
@@ -1662,6 +1788,9 @@
       <c r="H16">
         <v>0</v>
       </c>
+      <c r="Q16" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="str">
@@ -1700,6 +1829,9 @@
       <c r="M17" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q17" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="str">
@@ -1738,6 +1870,9 @@
       <c r="M18" t="str">
         <v>05/21/2026</v>
       </c>
+      <c r="Q18" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="str">
@@ -1758,6 +1893,9 @@
       <c r="H19">
         <v>0</v>
       </c>
+      <c r="Q19" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="str">
@@ -1778,6 +1916,9 @@
       <c r="H20">
         <v>0</v>
       </c>
+      <c r="Q20" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="str">
@@ -1797,6 +1938,9 @@
       </c>
       <c r="H21">
         <v>0</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Pendente</v>
       </c>
     </row>
   </sheetData>
@@ -1805,7 +1949,7 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1860,6 +2004,9 @@
       <c r="P1" t="str">
         <v>OBS. LUCIANA</v>
       </c>
+      <c r="Q1" t="str">
+        <v>ANDAMENTO</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1883,6 +2030,9 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="Q2" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="str">
@@ -1918,6 +2068,9 @@
       <c r="M3" t="str">
         <v>07/01/2026</v>
       </c>
+      <c r="Q3" t="str">
+        <v>Pendente</v>
+      </c>
       <c r="R3" t="str">
         <v>TURMA A</v>
       </c>
@@ -1956,6 +2109,9 @@
       <c r="M4" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Pendente</v>
+      </c>
       <c r="S4" t="str">
         <v>DAMAZ</v>
       </c>
@@ -1979,6 +2135,9 @@
       <c r="H5">
         <v>23</v>
       </c>
+      <c r="Q5" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
@@ -1998,6 +2157,9 @@
       </c>
       <c r="H6">
         <v>0</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Pendente</v>
       </c>
     </row>
   </sheetData>
@@ -2013,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:Q12"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -2061,6 +2223,9 @@
       <c r="P1" t="str">
         <v>OBS. LUCIANA</v>
       </c>
+      <c r="Q1" t="str">
+        <v>ANDAMENTO</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2084,6 +2249,9 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="Q2" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="str">
@@ -2119,6 +2287,9 @@
       <c r="M3" t="str">
         <v>07/01/2026</v>
       </c>
+      <c r="Q3" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="str">
@@ -2154,6 +2325,9 @@
       <c r="M4" t="str">
         <v>05/21/2025</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="str">
@@ -2174,6 +2348,9 @@
       <c r="H5">
         <v>23</v>
       </c>
+      <c r="Q5" t="str">
+        <v>Pendente</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="str">
@@ -2194,8 +2371,8 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>1</v>
+      <c r="Q6" t="str">
+        <v>Pendente</v>
       </c>
     </row>
     <row r="12">
@@ -2209,7 +2386,7 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -616,7 +616,7 @@
         <v>05/21/2026</v>
       </c>
       <c r="Q5" t="str">
-        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
+        <v>Pendente</v>
       </c>
     </row>
     <row r="6">
@@ -1042,14 +1042,8 @@
       <c r="J16">
         <v>3</v>
       </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
       <c r="Q16" t="str">
-        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
+        <v>Pendente</v>
       </c>
     </row>
     <row r="17">
@@ -1121,12 +1115,6 @@
       <c r="J18">
         <v>5</v>
       </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
       <c r="Q18" t="str">
         <v>Pendente</v>
       </c>
@@ -1151,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
   </sheetData>
@@ -1736,6 +1724,15 @@
       <c r="H14">
         <v>0</v>
       </c>
+      <c r="I14">
+        <v>6</v>
+      </c>
+      <c r="J14">
+        <v>17</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
       <c r="Q14" t="str">
         <v>Pendente</v>
       </c>
@@ -1762,6 +1759,12 @@
       <c r="H15">
         <v>0</v>
       </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
       <c r="Q15" t="str">
         <v>Pendente</v>
       </c>
@@ -1788,6 +1791,12 @@
       <c r="H16">
         <v>0</v>
       </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
       <c r="Q16" t="str">
         <v>Pendente</v>
       </c>
@@ -1893,6 +1902,12 @@
       <c r="H19">
         <v>0</v>
       </c>
+      <c r="I19">
+        <v>8</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
       <c r="Q19" t="str">
         <v>Pendente</v>
       </c>
@@ -1916,6 +1931,9 @@
       <c r="H20">
         <v>0</v>
       </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
       <c r="Q20" t="str">
         <v>Pendente</v>
       </c>
@@ -1940,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
   </sheetData>
@@ -2135,6 +2153,15 @@
       <c r="H5">
         <v>23</v>
       </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
       <c r="Q5" t="str">
         <v>Pendente</v>
       </c>
@@ -2156,6 +2183,9 @@
         <v>0</v>
       </c>
       <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
       <c r="Q6" t="str">
@@ -2249,6 +2279,12 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="Q2" t="str">
         <v>Pendente</v>
       </c>
@@ -2349,7 +2385,7 @@
         <v>23</v>
       </c>
       <c r="Q5" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="6">
@@ -2372,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="12">

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -1734,7 +1734,7 @@
         <v>4</v>
       </c>
       <c r="Q14" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="15">
@@ -1766,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="Q15" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="16">
@@ -1798,7 +1798,7 @@
         <v>2</v>
       </c>
       <c r="Q16" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="17">
@@ -1909,7 +1909,7 @@
         <v>2</v>
       </c>
       <c r="Q19" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="20">
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="21">
@@ -2163,7 +2163,7 @@
         <v>15</v>
       </c>
       <c r="Q5" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="6">
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
   </sheetData>

--- a/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
+++ b/CONTROLE RECURSOS HUMANOS - PLANO DE AULA.xlsx
@@ -1043,7 +1043,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="17">
@@ -1116,7 +1116,7 @@
         <v>5</v>
       </c>
       <c r="Q18" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="19">
@@ -2048,8 +2048,14 @@
       <c r="H2">
         <v>15</v>
       </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
       <c r="Q2" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="3">
@@ -2286,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="str">
-        <v>Pendente</v>
+        <v>PendenteRevisado para envioEnviadoSem plano de aula</v>
       </c>
     </row>
     <row r="3">
